--- a/database/19-SER_hh_tes.xlsx
+++ b/database/19-SER_hh_tes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\_BACKUPS_\Herramienta\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\git\buildings\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA7D5FE-187A-44B7-AC5A-AE3D446B4900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F972C1-A8A3-4CB7-AC3C-FEFFCC532DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2BE9BE4-B351-4E0F-8212-687FBB0A1F0E}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
   <si>
     <t>AT</t>
   </si>
@@ -217,154 +217,157 @@
     <t>Hydrogen</t>
   </si>
   <si>
-    <t>_Electricity in circulation</t>
-  </si>
-  <si>
     <t>Electricity in circulation</t>
   </si>
   <si>
+    <t>Space cooling</t>
+  </si>
+  <si>
+    <t>Space cooling_Gas heat pumps</t>
+  </si>
+  <si>
+    <t>Space cooling_Electric space cooling</t>
+  </si>
+  <si>
+    <t>Electric space cooling</t>
+  </si>
+  <si>
+    <t>_Water heating</t>
+  </si>
+  <si>
+    <t>Water heating</t>
+  </si>
+  <si>
+    <t>Water heating_Solids</t>
+  </si>
+  <si>
+    <t>Water heating_Liquified petroleum gas (LPG)</t>
+  </si>
+  <si>
+    <t>Water heating_Diesel oil</t>
+  </si>
+  <si>
+    <t>Water heating_Natural gas</t>
+  </si>
+  <si>
+    <t>Water heating_Biomass</t>
+  </si>
+  <si>
+    <t>Water heating_Geothermal</t>
+  </si>
+  <si>
+    <t>Water heating_Distributed heat</t>
+  </si>
+  <si>
+    <t>Water heating_Electricity</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Water heating_BioOil</t>
+  </si>
+  <si>
+    <t>Water heating_BioGas</t>
+  </si>
+  <si>
+    <t>Water heating_Hydrogen</t>
+  </si>
+  <si>
+    <t>Water heating_Solar</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>_Cooking</t>
+  </si>
+  <si>
+    <t>Cooking</t>
+  </si>
+  <si>
+    <t>Cooking_Solids</t>
+  </si>
+  <si>
+    <t>Cooking_Liquified petroleum gas (LPG)</t>
+  </si>
+  <si>
+    <t>Cooking_Natural gas</t>
+  </si>
+  <si>
+    <t>Cooking_Biomass</t>
+  </si>
+  <si>
+    <t>Cooking_Electricity</t>
+  </si>
+  <si>
+    <t>_Appliances</t>
+  </si>
+  <si>
+    <t>Appliances</t>
+  </si>
+  <si>
+    <t>Appliances_Electricity</t>
+  </si>
+  <si>
+    <t>_Lighting</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>Lighting_Electricity</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>MK</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>UA</t>
+  </si>
+  <si>
+    <t>XK</t>
+  </si>
+  <si>
+    <t>Energy service_Fuel</t>
+  </si>
+  <si>
+    <t>Energy service</t>
+  </si>
+  <si>
+    <t>_Space heating</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Space heating_Electricity in circulation</t>
+  </si>
+  <si>
     <t>_Space cooling</t>
-  </si>
-  <si>
-    <t>Space cooling</t>
-  </si>
-  <si>
-    <t>Space cooling_Gas heat pumps</t>
-  </si>
-  <si>
-    <t>Space cooling_Electric space cooling</t>
-  </si>
-  <si>
-    <t>Electric space cooling</t>
-  </si>
-  <si>
-    <t>_Water heating</t>
-  </si>
-  <si>
-    <t>Water heating</t>
-  </si>
-  <si>
-    <t>Water heating_Solids</t>
-  </si>
-  <si>
-    <t>Water heating_Liquified petroleum gas (LPG)</t>
-  </si>
-  <si>
-    <t>Water heating_Diesel oil</t>
-  </si>
-  <si>
-    <t>Water heating_Natural gas</t>
-  </si>
-  <si>
-    <t>Water heating_Biomass</t>
-  </si>
-  <si>
-    <t>Water heating_Geothermal</t>
-  </si>
-  <si>
-    <t>Water heating_Distributed heat</t>
-  </si>
-  <si>
-    <t>Water heating_Electricity</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Water heating_BioOil</t>
-  </si>
-  <si>
-    <t>Water heating_BioGas</t>
-  </si>
-  <si>
-    <t>Water heating_Hydrogen</t>
-  </si>
-  <si>
-    <t>Water heating_Solar</t>
-  </si>
-  <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>_Cooking</t>
-  </si>
-  <si>
-    <t>Cooking</t>
-  </si>
-  <si>
-    <t>Cooking_Solids</t>
-  </si>
-  <si>
-    <t>Cooking_Liquified petroleum gas (LPG)</t>
-  </si>
-  <si>
-    <t>Cooking_Natural gas</t>
-  </si>
-  <si>
-    <t>Cooking_Biomass</t>
-  </si>
-  <si>
-    <t>Cooking_Electricity</t>
-  </si>
-  <si>
-    <t>_Appliances</t>
-  </si>
-  <si>
-    <t>Appliances</t>
-  </si>
-  <si>
-    <t>Appliances_Electricity</t>
-  </si>
-  <si>
-    <t>_Lighting</t>
-  </si>
-  <si>
-    <t>Lighting</t>
-  </si>
-  <si>
-    <t>Lighting_Electricity</t>
-  </si>
-  <si>
-    <t>AL</t>
-  </si>
-  <si>
-    <t>CH</t>
-  </si>
-  <si>
-    <t>IS</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>MK</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>RS</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>UA</t>
-  </si>
-  <si>
-    <t>XK</t>
-  </si>
-  <si>
-    <t>Energy service_Fuel</t>
-  </si>
-  <si>
-    <t>Energy service</t>
-  </si>
-  <si>
-    <t>_Space heating</t>
   </si>
   <si>
     <t>Water heating_Advanced electric heating</t>
@@ -990,30 +993,32 @@
   <sheetPr codeName="Hoja37">
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:DF43"/>
+  <dimension ref="A1:DG43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="40.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
     <col min="4" max="30" width="10.7109375" style="1" customWidth="1"/>
-    <col min="31" max="40" width="9.140625" style="1" customWidth="1"/>
-    <col min="41" max="41" width="10.7109375" style="1" customWidth="1"/>
-    <col min="42" max="108" width="9.140625" style="1" customWidth="1"/>
-    <col min="109" max="109" width="2.7109375" style="1" customWidth="1"/>
-    <col min="110" max="110" width="10.7109375" style="5" customWidth="1"/>
-    <col min="111" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="39" width="9.140625" style="1" customWidth="1"/>
+    <col min="40" max="40" width="10.7109375" style="1" customWidth="1"/>
+    <col min="41" max="41" width="9.140625" style="1" customWidth="1"/>
+    <col min="42" max="42" width="10.7109375" style="1" customWidth="1"/>
+    <col min="43" max="109" width="9.140625" style="1" customWidth="1"/>
+    <col min="110" max="110" width="2.7109375" style="1" customWidth="1"/>
+    <col min="111" max="111" width="10.7109375" style="5" customWidth="1"/>
+    <col min="112" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:110" ht="12.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:111" ht="12.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -1025,7 +1030,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -1064,13 +1069,13 @@
         <v>15</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="U1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="W1" s="3" t="s">
         <v>17</v>
@@ -1082,10 +1087,10 @@
         <v>19</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AB1" s="3" t="s">
         <v>20</v>
@@ -1094,7 +1099,7 @@
         <v>21</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AE1" s="3" t="s">
         <v>22</v>
@@ -1106,7 +1111,7 @@
         <v>24</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AI1" s="3" t="s">
         <v>25</v>
@@ -1118,22 +1123,25 @@
         <v>27</v>
       </c>
       <c r="AL1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="AO1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AM1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="DF1" s="4"/>
+      <c r="DG1" s="4"/>
     </row>
-    <row r="2" spans="1:110" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:111" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>28</v>
@@ -1255,9 +1263,12 @@
       <c r="AO2" s="7">
         <v>1</v>
       </c>
-      <c r="DF2" s="8"/>
+      <c r="AP2" s="7">
+        <v>1</v>
+      </c>
+      <c r="DG2" s="8"/>
     </row>
-    <row r="3" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -1381,9 +1392,12 @@
       <c r="AO3" s="10">
         <v>9.8865706760057504E-3</v>
       </c>
-      <c r="DF3" s="11"/>
+      <c r="AP3" s="10">
+        <v>9.8865706760057504E-3</v>
+      </c>
+      <c r="DG3" s="11"/>
     </row>
-    <row r="4" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1507,9 +1521,12 @@
       <c r="AO4" s="10">
         <v>2.8124305347310245E-3</v>
       </c>
-      <c r="DF4" s="11"/>
+      <c r="AP4" s="10">
+        <v>2.8124305347310245E-3</v>
+      </c>
+      <c r="DG4" s="11"/>
     </row>
-    <row r="5" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -1633,9 +1650,12 @@
       <c r="AO5" s="10">
         <v>0.11181171672042593</v>
       </c>
-      <c r="DF5" s="11"/>
+      <c r="AP5" s="10">
+        <v>0.11181171672042593</v>
+      </c>
+      <c r="DG5" s="11"/>
     </row>
-    <row r="6" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1759,9 +1779,12 @@
       <c r="AO6" s="10">
         <v>7.8240070237200754E-3</v>
       </c>
-      <c r="DF6" s="11"/>
+      <c r="AP6" s="10">
+        <v>7.8240070237200754E-3</v>
+      </c>
+      <c r="DG6" s="11"/>
     </row>
-    <row r="7" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
@@ -1885,9 +1908,12 @@
       <c r="AO7" s="10">
         <v>0.38932817376553347</v>
       </c>
-      <c r="DF7" s="11"/>
+      <c r="AP7" s="10">
+        <v>0.38932817376553347</v>
+      </c>
+      <c r="DG7" s="11"/>
     </row>
-    <row r="8" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -2011,9 +2037,12 @@
       <c r="AO8" s="10">
         <v>4.6574578819737839E-2</v>
       </c>
-      <c r="DF8" s="11"/>
+      <c r="AP8" s="10">
+        <v>4.6574578819737839E-2</v>
+      </c>
+      <c r="DG8" s="11"/>
     </row>
-    <row r="9" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -2137,9 +2166,12 @@
       <c r="AO9" s="10">
         <v>4.034998767641032E-3</v>
       </c>
-      <c r="DF9" s="11"/>
+      <c r="AP9" s="10">
+        <v>4.034998767641032E-3</v>
+      </c>
+      <c r="DG9" s="11"/>
     </row>
-    <row r="10" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>43</v>
       </c>
@@ -2263,9 +2295,12 @@
       <c r="AO10" s="10">
         <v>0.14520037219225398</v>
       </c>
-      <c r="DF10" s="11"/>
+      <c r="AP10" s="10">
+        <v>0.14520037219225398</v>
+      </c>
+      <c r="DG10" s="11"/>
     </row>
-    <row r="11" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
@@ -2389,9 +2424,12 @@
       <c r="AO11" s="10">
         <v>0.12497967123142001</v>
       </c>
-      <c r="DF11" s="11"/>
+      <c r="AP11" s="10">
+        <v>0.12497967123142001</v>
+      </c>
+      <c r="DG11" s="11"/>
     </row>
-    <row r="12" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>47</v>
       </c>
@@ -2515,9 +2553,12 @@
       <c r="AO12" s="10">
         <v>0.14847420484978488</v>
       </c>
-      <c r="DF12" s="12"/>
+      <c r="AP12" s="10">
+        <v>0.14847420484978488</v>
+      </c>
+      <c r="DG12" s="12"/>
     </row>
-    <row r="13" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>49</v>
       </c>
@@ -2641,9 +2682,12 @@
       <c r="AO13" s="10">
         <v>0</v>
       </c>
-      <c r="DF13" s="12"/>
+      <c r="AP13" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG13" s="12"/>
     </row>
-    <row r="14" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>51</v>
       </c>
@@ -2767,9 +2811,12 @@
       <c r="AO14" s="10">
         <v>0</v>
       </c>
-      <c r="DF14" s="12"/>
+      <c r="AP14" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG14" s="12"/>
     </row>
-    <row r="15" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>53</v>
       </c>
@@ -2893,14 +2940,17 @@
       <c r="AO15" s="10">
         <v>0</v>
       </c>
-      <c r="DF15" s="12"/>
+      <c r="AP15" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG15" s="12"/>
     </row>
-    <row r="16" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>56</v>
       </c>
       <c r="C16" s="10">
         <v>9.0732754187459411E-3</v>
@@ -3019,14 +3069,17 @@
       <c r="AO16" s="10">
         <v>9.0732754187459411E-3</v>
       </c>
-      <c r="DF16" s="14"/>
+      <c r="AP16" s="10">
+        <v>9.0732754187459411E-3</v>
+      </c>
+      <c r="DG16" s="14"/>
     </row>
-    <row r="17" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C17" s="15">
         <v>0.37016733475089147</v>
@@ -3145,11 +3198,14 @@
       <c r="AO17" s="15">
         <v>0.37016733475089147</v>
       </c>
-      <c r="DF17" s="8"/>
+      <c r="AP17" s="15">
+        <v>0.37016733475089147</v>
+      </c>
+      <c r="DG17" s="8"/>
     </row>
-    <row r="18" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>36</v>
@@ -3271,14 +3327,17 @@
       <c r="AO18" s="10">
         <v>1.4777483315545546E-2</v>
       </c>
-      <c r="DF18" s="11"/>
+      <c r="AP18" s="10">
+        <v>1.4777483315545546E-2</v>
+      </c>
+      <c r="DG18" s="11"/>
     </row>
-    <row r="19" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C19" s="10">
         <v>0.98522251668445449</v>
@@ -3397,137 +3456,143 @@
       <c r="AO19" s="10">
         <v>0.98522251668445449</v>
       </c>
-      <c r="DF19" s="11"/>
+      <c r="AP19" s="10">
+        <v>0.98522251668445449</v>
+      </c>
+      <c r="DG19" s="11"/>
     </row>
-    <row r="20" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7">
+        <v>1</v>
+      </c>
+      <c r="I20" s="7">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7">
+        <v>1</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1</v>
+      </c>
+      <c r="L20" s="7">
+        <v>1</v>
+      </c>
+      <c r="M20" s="7">
+        <v>1</v>
+      </c>
+      <c r="N20" s="7">
+        <v>1</v>
+      </c>
+      <c r="O20" s="7">
+        <v>1</v>
+      </c>
+      <c r="P20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>1</v>
+      </c>
+      <c r="R20" s="7">
+        <v>1</v>
+      </c>
+      <c r="S20" s="7">
+        <v>1</v>
+      </c>
+      <c r="T20" s="7">
+        <v>1</v>
+      </c>
+      <c r="U20" s="7">
+        <v>1</v>
+      </c>
+      <c r="V20" s="7">
+        <v>1</v>
+      </c>
+      <c r="W20" s="7">
+        <v>1</v>
+      </c>
+      <c r="X20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP20" s="7">
+        <v>1</v>
+      </c>
+      <c r="DG20" s="8"/>
+    </row>
+    <row r="21" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="7">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7">
-        <v>1</v>
-      </c>
-      <c r="I20" s="7">
-        <v>1</v>
-      </c>
-      <c r="J20" s="7">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7">
-        <v>1</v>
-      </c>
-      <c r="L20" s="7">
-        <v>1</v>
-      </c>
-      <c r="M20" s="7">
-        <v>1</v>
-      </c>
-      <c r="N20" s="7">
-        <v>1</v>
-      </c>
-      <c r="O20" s="7">
-        <v>1</v>
-      </c>
-      <c r="P20" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="7">
-        <v>1</v>
-      </c>
-      <c r="R20" s="7">
-        <v>1</v>
-      </c>
-      <c r="S20" s="7">
-        <v>1</v>
-      </c>
-      <c r="T20" s="7">
-        <v>1</v>
-      </c>
-      <c r="U20" s="7">
-        <v>1</v>
-      </c>
-      <c r="V20" s="7">
-        <v>1</v>
-      </c>
-      <c r="W20" s="7">
-        <v>1</v>
-      </c>
-      <c r="X20" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN20" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO20" s="7">
-        <v>1</v>
-      </c>
-      <c r="DF20" s="8"/>
-    </row>
-    <row r="21" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>30</v>
@@ -3649,11 +3714,14 @@
       <c r="AO21" s="10">
         <v>2.92455447401185E-3</v>
       </c>
-      <c r="DF21" s="11"/>
+      <c r="AP21" s="10">
+        <v>2.92455447401185E-3</v>
+      </c>
+      <c r="DG21" s="11"/>
     </row>
-    <row r="22" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>32</v>
@@ -3775,11 +3843,14 @@
       <c r="AO22" s="10">
         <v>1.2327117192137549E-2</v>
       </c>
-      <c r="DF22" s="11"/>
+      <c r="AP22" s="10">
+        <v>1.2327117192137549E-2</v>
+      </c>
+      <c r="DG22" s="11"/>
     </row>
-    <row r="23" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>34</v>
@@ -3901,11 +3972,14 @@
       <c r="AO23" s="10">
         <v>0.10031944776538876</v>
       </c>
-      <c r="DF23" s="11"/>
+      <c r="AP23" s="10">
+        <v>0.10031944776538876</v>
+      </c>
+      <c r="DG23" s="11"/>
     </row>
-    <row r="24" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>38</v>
@@ -4027,11 +4101,14 @@
       <c r="AO24" s="10">
         <v>0.34801337302759483</v>
       </c>
-      <c r="DF24" s="11"/>
+      <c r="AP24" s="10">
+        <v>0.34801337302759483</v>
+      </c>
+      <c r="DG24" s="11"/>
     </row>
-    <row r="25" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>40</v>
@@ -4153,11 +4230,14 @@
       <c r="AO25" s="10">
         <v>6.629431731802706E-3</v>
       </c>
-      <c r="DF25" s="11"/>
+      <c r="AP25" s="10">
+        <v>6.629431731802706E-3</v>
+      </c>
+      <c r="DG25" s="11"/>
     </row>
-    <row r="26" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>42</v>
@@ -4279,11 +4359,14 @@
       <c r="AO26" s="10">
         <v>0</v>
       </c>
-      <c r="DF26" s="11"/>
+      <c r="AP26" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG26" s="11"/>
     </row>
-    <row r="27" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>44</v>
@@ -4405,11 +4488,14 @@
       <c r="AO27" s="10">
         <v>0.1080837099681915</v>
       </c>
-      <c r="DF27" s="11"/>
+      <c r="AP27" s="10">
+        <v>0.1080837099681915</v>
+      </c>
+      <c r="DG27" s="11"/>
     </row>
-    <row r="28" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>46</v>
@@ -4531,14 +4617,17 @@
       <c r="AO28" s="10">
         <v>0</v>
       </c>
-      <c r="DF28" s="11"/>
+      <c r="AP28" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG28" s="11"/>
     </row>
-    <row r="29" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C29" s="10">
         <v>0.3899399826166125</v>
@@ -4657,11 +4746,14 @@
       <c r="AO29" s="10">
         <v>0.3899399826166125</v>
       </c>
-      <c r="DF29" s="12"/>
+      <c r="AP29" s="10">
+        <v>0.3899399826166125</v>
+      </c>
+      <c r="DG29" s="12"/>
     </row>
-    <row r="30" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>50</v>
@@ -4783,11 +4875,14 @@
       <c r="AO30" s="10">
         <v>0</v>
       </c>
-      <c r="DF30" s="12"/>
+      <c r="AP30" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG30" s="12"/>
     </row>
-    <row r="31" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>52</v>
@@ -4909,11 +5004,14 @@
       <c r="AO31" s="10">
         <v>0</v>
       </c>
-      <c r="DF31" s="12"/>
+      <c r="AP31" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG31" s="12"/>
     </row>
-    <row r="32" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>54</v>
@@ -5035,14 +5133,17 @@
       <c r="AO32" s="10">
         <v>0</v>
       </c>
-      <c r="DF32" s="12"/>
+      <c r="AP32" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG32" s="12"/>
     </row>
-    <row r="33" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C33" s="10">
         <v>3.1762383224260268E-2</v>
@@ -5161,137 +5262,143 @@
       <c r="AO33" s="10">
         <v>3.1762383224260268E-2</v>
       </c>
-      <c r="DF33" s="16"/>
+      <c r="AP33" s="10">
+        <v>3.1762383224260268E-2</v>
+      </c>
+      <c r="DG33" s="16"/>
     </row>
-    <row r="34" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7">
+        <v>1</v>
+      </c>
+      <c r="H34" s="7">
+        <v>1</v>
+      </c>
+      <c r="I34" s="7">
+        <v>1</v>
+      </c>
+      <c r="J34" s="7">
+        <v>1</v>
+      </c>
+      <c r="K34" s="7">
+        <v>1</v>
+      </c>
+      <c r="L34" s="7">
+        <v>1</v>
+      </c>
+      <c r="M34" s="7">
+        <v>1</v>
+      </c>
+      <c r="N34" s="7">
+        <v>1</v>
+      </c>
+      <c r="O34" s="7">
+        <v>1</v>
+      </c>
+      <c r="P34" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="7">
+        <v>1</v>
+      </c>
+      <c r="R34" s="7">
+        <v>1</v>
+      </c>
+      <c r="S34" s="7">
+        <v>1</v>
+      </c>
+      <c r="T34" s="7">
+        <v>1</v>
+      </c>
+      <c r="U34" s="7">
+        <v>1</v>
+      </c>
+      <c r="V34" s="7">
+        <v>1</v>
+      </c>
+      <c r="W34" s="7">
+        <v>1</v>
+      </c>
+      <c r="X34" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO34" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP34" s="7">
+        <v>1</v>
+      </c>
+      <c r="DG34" s="8"/>
+    </row>
+    <row r="35" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="7">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1</v>
-      </c>
-      <c r="F34" s="7">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7">
-        <v>1</v>
-      </c>
-      <c r="I34" s="7">
-        <v>1</v>
-      </c>
-      <c r="J34" s="7">
-        <v>1</v>
-      </c>
-      <c r="K34" s="7">
-        <v>1</v>
-      </c>
-      <c r="L34" s="7">
-        <v>1</v>
-      </c>
-      <c r="M34" s="7">
-        <v>1</v>
-      </c>
-      <c r="N34" s="7">
-        <v>1</v>
-      </c>
-      <c r="O34" s="7">
-        <v>1</v>
-      </c>
-      <c r="P34" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="7">
-        <v>1</v>
-      </c>
-      <c r="R34" s="7">
-        <v>1</v>
-      </c>
-      <c r="S34" s="7">
-        <v>1</v>
-      </c>
-      <c r="T34" s="7">
-        <v>1</v>
-      </c>
-      <c r="U34" s="7">
-        <v>1</v>
-      </c>
-      <c r="V34" s="7">
-        <v>1</v>
-      </c>
-      <c r="W34" s="7">
-        <v>1</v>
-      </c>
-      <c r="X34" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN34" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO34" s="7">
-        <v>1</v>
-      </c>
-      <c r="DF34" s="8"/>
-    </row>
-    <row r="35" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>30</v>
@@ -5413,11 +5520,14 @@
       <c r="AO35" s="10">
         <v>0</v>
       </c>
-      <c r="DF35" s="11"/>
+      <c r="AP35" s="10">
+        <v>0</v>
+      </c>
+      <c r="DG35" s="11"/>
     </row>
-    <row r="36" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>32</v>
@@ -5539,11 +5649,14 @@
       <c r="AO36" s="10">
         <v>6.736688066584702E-2</v>
       </c>
-      <c r="DF36" s="11"/>
+      <c r="AP36" s="10">
+        <v>6.736688066584702E-2</v>
+      </c>
+      <c r="DG36" s="11"/>
     </row>
-    <row r="37" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>38</v>
@@ -5665,11 +5778,14 @@
       <c r="AO37" s="10">
         <v>0.41585603944492661</v>
       </c>
-      <c r="DF37" s="11"/>
+      <c r="AP37" s="10">
+        <v>0.41585603944492661</v>
+      </c>
+      <c r="DG37" s="11"/>
     </row>
-    <row r="38" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>40</v>
@@ -5791,14 +5907,17 @@
       <c r="AO38" s="10">
         <v>2.9625969546928938E-3</v>
       </c>
-      <c r="DF38" s="11"/>
+      <c r="AP38" s="10">
+        <v>2.9625969546928938E-3</v>
+      </c>
+      <c r="DG38" s="11"/>
     </row>
-    <row r="39" spans="1:110" ht="11.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:111" ht="11.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C39" s="10">
         <v>0.51381448293453325</v>
@@ -5917,390 +6036,402 @@
       <c r="AO39" s="10">
         <v>0.51381448293453325</v>
       </c>
-      <c r="DF39" s="18"/>
+      <c r="AP39" s="10">
+        <v>0.51381448293453325</v>
+      </c>
+      <c r="DG39" s="18"/>
     </row>
-    <row r="40" spans="1:110" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:111" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="7">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1</v>
+      </c>
+      <c r="F40" s="7">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1</v>
+      </c>
+      <c r="H40" s="7">
+        <v>1</v>
+      </c>
+      <c r="I40" s="7">
+        <v>1</v>
+      </c>
+      <c r="J40" s="7">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7">
+        <v>1</v>
+      </c>
+      <c r="L40" s="7">
+        <v>1</v>
+      </c>
+      <c r="M40" s="7">
+        <v>1</v>
+      </c>
+      <c r="N40" s="7">
+        <v>1</v>
+      </c>
+      <c r="O40" s="7">
+        <v>1</v>
+      </c>
+      <c r="P40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>1</v>
+      </c>
+      <c r="R40" s="7">
+        <v>1</v>
+      </c>
+      <c r="S40" s="7">
+        <v>1</v>
+      </c>
+      <c r="T40" s="7">
+        <v>1</v>
+      </c>
+      <c r="U40" s="7">
+        <v>1</v>
+      </c>
+      <c r="V40" s="7">
+        <v>1</v>
+      </c>
+      <c r="W40" s="7">
+        <v>1</v>
+      </c>
+      <c r="X40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP40" s="7">
+        <v>1</v>
+      </c>
+      <c r="DG40" s="12"/>
+    </row>
+    <row r="41" spans="1:111" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B41" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="19">
+        <v>1</v>
+      </c>
+      <c r="D41" s="19">
+        <v>1</v>
+      </c>
+      <c r="E41" s="19">
+        <v>1</v>
+      </c>
+      <c r="F41" s="19">
+        <v>1</v>
+      </c>
+      <c r="G41" s="19">
+        <v>1</v>
+      </c>
+      <c r="H41" s="19">
+        <v>1</v>
+      </c>
+      <c r="I41" s="19">
+        <v>1</v>
+      </c>
+      <c r="J41" s="19">
+        <v>1</v>
+      </c>
+      <c r="K41" s="19">
+        <v>1</v>
+      </c>
+      <c r="L41" s="19">
+        <v>1</v>
+      </c>
+      <c r="M41" s="19">
+        <v>1</v>
+      </c>
+      <c r="N41" s="19">
+        <v>1</v>
+      </c>
+      <c r="O41" s="19">
+        <v>1</v>
+      </c>
+      <c r="P41" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="19">
+        <v>1</v>
+      </c>
+      <c r="R41" s="19">
+        <v>1</v>
+      </c>
+      <c r="S41" s="19">
+        <v>1</v>
+      </c>
+      <c r="T41" s="19">
+        <v>1</v>
+      </c>
+      <c r="U41" s="19">
+        <v>1</v>
+      </c>
+      <c r="V41" s="19">
+        <v>1</v>
+      </c>
+      <c r="W41" s="19">
+        <v>1</v>
+      </c>
+      <c r="X41" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AD41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AH41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AL41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AM41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="19">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:111" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="7">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1</v>
-      </c>
-      <c r="F40" s="7">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7">
-        <v>1</v>
-      </c>
-      <c r="H40" s="7">
-        <v>1</v>
-      </c>
-      <c r="I40" s="7">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7">
-        <v>1</v>
-      </c>
-      <c r="L40" s="7">
-        <v>1</v>
-      </c>
-      <c r="M40" s="7">
-        <v>1</v>
-      </c>
-      <c r="N40" s="7">
-        <v>1</v>
-      </c>
-      <c r="O40" s="7">
-        <v>1</v>
-      </c>
-      <c r="P40" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="7">
-        <v>1</v>
-      </c>
-      <c r="R40" s="7">
-        <v>1</v>
-      </c>
-      <c r="S40" s="7">
-        <v>1</v>
-      </c>
-      <c r="T40" s="7">
-        <v>1</v>
-      </c>
-      <c r="U40" s="7">
-        <v>1</v>
-      </c>
-      <c r="V40" s="7">
-        <v>1</v>
-      </c>
-      <c r="W40" s="7">
-        <v>1</v>
-      </c>
-      <c r="X40" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO40" s="7">
-        <v>1</v>
-      </c>
-      <c r="DF40" s="12"/>
+      <c r="B42" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1</v>
+      </c>
+      <c r="H42" s="7">
+        <v>1</v>
+      </c>
+      <c r="I42" s="7">
+        <v>1</v>
+      </c>
+      <c r="J42" s="7">
+        <v>1</v>
+      </c>
+      <c r="K42" s="7">
+        <v>1</v>
+      </c>
+      <c r="L42" s="7">
+        <v>1</v>
+      </c>
+      <c r="M42" s="7">
+        <v>1</v>
+      </c>
+      <c r="N42" s="7">
+        <v>1</v>
+      </c>
+      <c r="O42" s="7">
+        <v>1</v>
+      </c>
+      <c r="P42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>1</v>
+      </c>
+      <c r="R42" s="7">
+        <v>1</v>
+      </c>
+      <c r="S42" s="7">
+        <v>1</v>
+      </c>
+      <c r="T42" s="7">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7">
+        <v>1</v>
+      </c>
+      <c r="V42" s="7">
+        <v>1</v>
+      </c>
+      <c r="W42" s="7">
+        <v>1</v>
+      </c>
+      <c r="X42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="41" spans="1:110" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>87</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="19">
-        <v>1</v>
-      </c>
-      <c r="D41" s="19">
-        <v>1</v>
-      </c>
-      <c r="E41" s="19">
-        <v>1</v>
-      </c>
-      <c r="F41" s="19">
-        <v>1</v>
-      </c>
-      <c r="G41" s="19">
-        <v>1</v>
-      </c>
-      <c r="H41" s="19">
-        <v>1</v>
-      </c>
-      <c r="I41" s="19">
-        <v>1</v>
-      </c>
-      <c r="J41" s="19">
-        <v>1</v>
-      </c>
-      <c r="K41" s="19">
-        <v>1</v>
-      </c>
-      <c r="L41" s="19">
-        <v>1</v>
-      </c>
-      <c r="M41" s="19">
-        <v>1</v>
-      </c>
-      <c r="N41" s="19">
-        <v>1</v>
-      </c>
-      <c r="O41" s="19">
-        <v>1</v>
-      </c>
-      <c r="P41" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="19">
-        <v>1</v>
-      </c>
-      <c r="R41" s="19">
-        <v>1</v>
-      </c>
-      <c r="S41" s="19">
-        <v>1</v>
-      </c>
-      <c r="T41" s="19">
-        <v>1</v>
-      </c>
-      <c r="U41" s="19">
-        <v>1</v>
-      </c>
-      <c r="V41" s="19">
-        <v>1</v>
-      </c>
-      <c r="W41" s="19">
-        <v>1</v>
-      </c>
-      <c r="X41" s="19">
-        <v>1</v>
-      </c>
-      <c r="Y41" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AK41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AL41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AM41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AN41" s="19">
-        <v>1</v>
-      </c>
-      <c r="AO41" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:110" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="43" spans="1:111" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>88</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1</v>
-      </c>
-      <c r="F42" s="7">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7">
-        <v>1</v>
-      </c>
-      <c r="H42" s="7">
-        <v>1</v>
-      </c>
-      <c r="I42" s="7">
-        <v>1</v>
-      </c>
-      <c r="J42" s="7">
-        <v>1</v>
-      </c>
-      <c r="K42" s="7">
-        <v>1</v>
-      </c>
-      <c r="L42" s="7">
-        <v>1</v>
-      </c>
-      <c r="M42" s="7">
-        <v>1</v>
-      </c>
-      <c r="N42" s="7">
-        <v>1</v>
-      </c>
-      <c r="O42" s="7">
-        <v>1</v>
-      </c>
-      <c r="P42" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="7">
-        <v>1</v>
-      </c>
-      <c r="R42" s="7">
-        <v>1</v>
-      </c>
-      <c r="S42" s="7">
-        <v>1</v>
-      </c>
-      <c r="T42" s="7">
-        <v>1</v>
-      </c>
-      <c r="U42" s="7">
-        <v>1</v>
-      </c>
-      <c r="V42" s="7">
-        <v>1</v>
-      </c>
-      <c r="W42" s="7">
-        <v>1</v>
-      </c>
-      <c r="X42" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO42" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:110" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
       <c r="B43" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C43" s="19">
         <v>1</v>
@@ -6417,6 +6548,9 @@
         <v>1</v>
       </c>
       <c r="AO43" s="19">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="19">
         <v>1</v>
       </c>
     </row>

--- a/database/19-SER_hh_tes.xlsx
+++ b/database/19-SER_hh_tes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\git\buildings\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnalia365-my.sharepoint.com/personal/nekane_hermoso_tecnalia_com/Documents/Documentos/Proyectos/iDesignRES/Enerkad/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60F972C1-A8A3-4CB7-AC3C-FEFFCC532DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{5B8C032F-270D-45F3-94EA-C0420D567880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{154EAF98-5150-46D2-8E8F-901C885A92CC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2BE9BE4-B351-4E0F-8212-687FBB0A1F0E}"/>
   </bookViews>
@@ -693,6 +693,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -996,7 +1000,7 @@
   <dimension ref="A1:DG43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="35" style="1" customWidth="1"/>
     <col min="2" max="2" width="40.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="1" customWidth="1"/>
     <col min="4" max="30" width="10.7109375" style="1" customWidth="1"/>
@@ -1276,7 +1280,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="D3" s="10">
         <v>0</v>
@@ -1285,91 +1289,91 @@
         <v>0</v>
       </c>
       <c r="F3" s="10">
-        <v>3.2830478816799863E-3</v>
+        <v>2.3994050804555709E-3</v>
       </c>
       <c r="G3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="H3" s="10">
         <v>0</v>
       </c>
       <c r="I3" s="10">
-        <v>1.2086929677460476E-2</v>
+        <v>6.749563044960943E-3</v>
       </c>
       <c r="J3" s="10">
-        <v>5.0219397971968559E-5</v>
+        <v>4.5755219344918484E-3</v>
       </c>
       <c r="K3" s="10">
         <v>0</v>
       </c>
       <c r="L3" s="10">
-        <v>3.0108503673771389E-3</v>
+        <v>1.7580929496925871E-3</v>
       </c>
       <c r="M3" s="10">
-        <v>0</v>
+        <v>1.2293973142285829E-2</v>
       </c>
       <c r="N3" s="10">
         <v>0</v>
       </c>
       <c r="O3" s="10">
-        <v>1.1098225428899425E-3</v>
+        <v>1.1174236363845355E-3</v>
       </c>
       <c r="P3" s="10">
-        <v>2.8928789749938523E-3</v>
+        <v>3.2081816834472069E-3</v>
       </c>
       <c r="Q3" s="10">
         <v>0</v>
       </c>
       <c r="R3" s="10">
-        <v>8.5081417822702426E-4</v>
+        <v>6.0089766695683945E-4</v>
       </c>
       <c r="S3" s="10">
-        <v>2.1909607500420465E-4</v>
+        <v>2.3374239549433558E-4</v>
       </c>
       <c r="T3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="U3" s="10">
         <v>0</v>
       </c>
       <c r="V3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="W3" s="10">
-        <v>7.8321834100332555E-2</v>
+        <v>5.4032995542224585E-2</v>
       </c>
       <c r="X3" s="10">
         <v>0</v>
       </c>
       <c r="Y3" s="10">
-        <v>4.6713406261727659E-3</v>
+        <v>6.8610082274370397E-3</v>
       </c>
       <c r="Z3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AA3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AB3" s="10">
         <v>0</v>
       </c>
       <c r="AC3" s="10">
-        <v>7.4727171195715239E-4</v>
+        <v>2.4061662962202579E-3</v>
       </c>
       <c r="AD3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AE3" s="10">
-        <v>0.117962402833553</v>
+        <v>5.0482616875163276E-2</v>
       </c>
       <c r="AF3" s="10">
         <v>0</v>
       </c>
       <c r="AG3" s="10">
-        <v>1.3724032504375475E-4</v>
+        <v>4.5932316951162087E-5</v>
       </c>
       <c r="AH3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AI3" s="10">
         <v>0</v>
@@ -1378,22 +1382,22 @@
         <v>0</v>
       </c>
       <c r="AK3" s="10">
-        <v>6.6665063937059219E-2</v>
+        <v>4.4988124045815647E-2</v>
       </c>
       <c r="AL3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AM3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AN3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AO3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="AP3" s="10">
-        <v>9.8865706760057504E-3</v>
+        <v>6.2888683716806259E-3</v>
       </c>
       <c r="DG3" s="11"/>
     </row>
@@ -1405,7 +1409,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="D4" s="10">
         <v>0</v>
@@ -1417,7 +1421,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="H4" s="10">
         <v>0</v>
@@ -1456,13 +1460,13 @@
         <v>0</v>
       </c>
       <c r="T4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="U4" s="10">
-        <v>1.7966043474288106E-2</v>
+        <v>1.4852691421851864E-2</v>
       </c>
       <c r="V4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="W4" s="10">
         <v>0</v>
@@ -1474,19 +1478,19 @@
         <v>0</v>
       </c>
       <c r="Z4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AA4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AB4" s="10">
-        <v>5.532701281278269E-2</v>
+        <v>3.4727653800094634E-2</v>
       </c>
       <c r="AC4" s="10">
         <v>0</v>
       </c>
       <c r="AD4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AE4" s="10">
         <v>0</v>
@@ -1498,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="AH4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AI4" s="10">
         <v>0</v>
@@ -1510,19 +1514,19 @@
         <v>0</v>
       </c>
       <c r="AL4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AM4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AN4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AO4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="AP4" s="10">
-        <v>2.8124305347310245E-3</v>
+        <v>2.7678259344435805E-3</v>
       </c>
       <c r="DG4" s="11"/>
     </row>
@@ -1534,124 +1538,124 @@
         <v>34</v>
       </c>
       <c r="C5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="D5" s="10">
-        <v>0.11095432740756894</v>
+        <v>5.3469973219842634E-2</v>
       </c>
       <c r="E5" s="10">
-        <v>0.1792836295695967</v>
+        <v>0.15429686176191038</v>
       </c>
       <c r="F5" s="10">
-        <v>2.0016166299402526E-2</v>
+        <v>3.6765071320888333E-2</v>
       </c>
       <c r="G5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="H5" s="10">
-        <v>0.15769219601915288</v>
+        <v>0.14786550323117362</v>
       </c>
       <c r="I5" s="10">
-        <v>8.8871886567638923E-3</v>
+        <v>1.0224240538344167E-2</v>
       </c>
       <c r="J5" s="10">
-        <v>0.19795824675129672</v>
+        <v>0.10978599182294034</v>
       </c>
       <c r="K5" s="10">
-        <v>1.3630263699238726E-2</v>
+        <v>1.7446972059599514E-2</v>
       </c>
       <c r="L5" s="10">
-        <v>5.0450574433457469E-2</v>
+        <v>8.4540176652987631E-2</v>
       </c>
       <c r="M5" s="10">
-        <v>2.3480402107965894E-2</v>
+        <v>1.3792596452526933E-2</v>
       </c>
       <c r="N5" s="10">
-        <v>0.23348373742246203</v>
+        <v>0.15913308702644768</v>
       </c>
       <c r="O5" s="10">
-        <v>0.11508671672514914</v>
+        <v>0.10544636461854422</v>
       </c>
       <c r="P5" s="10">
-        <v>0.1392923142219322</v>
+        <v>0.15664086019970236</v>
       </c>
       <c r="Q5" s="10">
-        <v>3.2545735724778903E-2</v>
+        <v>4.3597088448592662E-2</v>
       </c>
       <c r="R5" s="10">
-        <v>2.7589098705739126E-2</v>
+        <v>2.6056848378465829E-2</v>
       </c>
       <c r="S5" s="10">
-        <v>0.11935944779157423</v>
+        <v>0.11079305429950975</v>
       </c>
       <c r="T5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="U5" s="10">
-        <v>1.2626567924737415E-2</v>
+        <v>1.6581188745174925E-2</v>
       </c>
       <c r="V5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="W5" s="10">
-        <v>6.4456775928186444E-3</v>
+        <v>9.9072739163438249E-3</v>
       </c>
       <c r="X5" s="10">
-        <v>0.21013270397616393</v>
+        <v>0.21774361040286525</v>
       </c>
       <c r="Y5" s="10">
-        <v>0.12198911319332764</v>
+        <v>0.15645945063904879</v>
       </c>
       <c r="Z5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AA5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AB5" s="10">
-        <v>0.19126650374080317</v>
+        <v>0.14414252877584985</v>
       </c>
       <c r="AC5" s="10">
-        <v>4.9213108540205067E-2</v>
+        <v>6.3213021318177645E-2</v>
       </c>
       <c r="AD5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AE5" s="10">
-        <v>6.3894480481412372E-2</v>
+        <v>3.944395006794596E-2</v>
       </c>
       <c r="AF5" s="10">
-        <v>2.8283173584950968E-2</v>
+        <v>1.5503380017871242E-2</v>
       </c>
       <c r="AG5" s="10">
-        <v>0.3059232265483588</v>
+        <v>0.2555563841666183</v>
       </c>
       <c r="AH5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AI5" s="10">
-        <v>6.9963385511032719E-2</v>
+        <v>3.4020002775606191E-2</v>
       </c>
       <c r="AJ5" s="10">
-        <v>0.17157473252232078</v>
+        <v>0.23618382541797062</v>
       </c>
       <c r="AK5" s="10">
-        <v>3.3411364888035963E-3</v>
+        <v>2.9072944919817626E-3</v>
       </c>
       <c r="AL5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AM5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AN5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AO5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="AP5" s="10">
-        <v>0.11181171672042593</v>
+        <v>8.3631642025994712E-2</v>
       </c>
       <c r="DG5" s="11"/>
     </row>
@@ -1663,64 +1667,64 @@
         <v>36</v>
       </c>
       <c r="C6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="D6" s="10">
-        <v>4.8917982288556872E-3</v>
+        <v>5.7078083362932797E-3</v>
       </c>
       <c r="E6" s="10">
-        <v>9.0417737186515863E-5</v>
+        <v>2.4890699895149928E-4</v>
       </c>
       <c r="F6" s="10">
         <v>0</v>
       </c>
       <c r="G6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="H6" s="10">
         <v>0</v>
       </c>
       <c r="I6" s="10">
-        <v>2.2019791697309213E-3</v>
+        <v>3.0985313769001516E-3</v>
       </c>
       <c r="J6" s="10">
-        <v>1.4939498725554975E-3</v>
+        <v>2.8126335104440917E-3</v>
       </c>
       <c r="K6" s="10">
-        <v>5.9469380249337128E-3</v>
+        <v>1.0368024459452433E-2</v>
       </c>
       <c r="L6" s="10">
         <v>0</v>
       </c>
       <c r="M6" s="10">
-        <v>2.1970074533994029E-2</v>
+        <v>2.4439391588512393E-2</v>
       </c>
       <c r="N6" s="10">
-        <v>2.07816336825105E-2</v>
+        <v>2.9622938900098036E-2</v>
       </c>
       <c r="O6" s="10">
         <v>0</v>
       </c>
       <c r="P6" s="10">
-        <v>1.2678888064900608E-2</v>
+        <v>7.3450696108930159E-3</v>
       </c>
       <c r="Q6" s="10">
         <v>0</v>
       </c>
       <c r="R6" s="10">
-        <v>1.0874147114224908E-4</v>
+        <v>2.4195576836707518E-4</v>
       </c>
       <c r="S6" s="10">
         <v>0</v>
       </c>
       <c r="T6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="U6" s="10">
-        <v>2.3949289718630713E-2</v>
+        <v>2.3951245234816128E-2</v>
       </c>
       <c r="V6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="W6" s="10">
         <v>0</v>
@@ -1732,31 +1736,31 @@
         <v>0</v>
       </c>
       <c r="Z6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AA6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AB6" s="10">
         <v>0</v>
       </c>
       <c r="AC6" s="10">
-        <v>3.5361685772427164E-3</v>
+        <v>5.7191395643257552E-3</v>
       </c>
       <c r="AD6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AE6" s="10">
-        <v>7.0559715629113124E-5</v>
+        <v>1.0965002897759664E-4</v>
       </c>
       <c r="AF6" s="10">
-        <v>3.6188866179016118E-3</v>
+        <v>3.7036867031427769E-3</v>
       </c>
       <c r="AG6" s="10">
         <v>0</v>
       </c>
       <c r="AH6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AI6" s="10">
         <v>0</v>
@@ -1765,22 +1769,22 @@
         <v>0</v>
       </c>
       <c r="AK6" s="10">
-        <v>1.0264995168757739E-3</v>
+        <v>2.0431623024031605E-3</v>
       </c>
       <c r="AL6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AM6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AN6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AO6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="AP6" s="10">
-        <v>7.8240070237200754E-3</v>
+        <v>8.5914741660087848E-3</v>
       </c>
       <c r="DG6" s="11"/>
     </row>
@@ -1792,124 +1796,124 @@
         <v>38</v>
       </c>
       <c r="C7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="D7" s="10">
-        <v>0.15841508153707082</v>
+        <v>0.12297009058457972</v>
       </c>
       <c r="E7" s="10">
-        <v>0.62119700221585605</v>
+        <v>0.55535812764009684</v>
       </c>
       <c r="F7" s="10">
-        <v>9.6588861183270258E-2</v>
+        <v>7.0000877653599664E-2</v>
       </c>
       <c r="G7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="H7" s="10">
-        <v>5.1980442615812573E-3</v>
+        <v>0</v>
       </c>
       <c r="I7" s="10">
-        <v>0.40030219073912243</v>
+        <v>0.37437760017435107</v>
       </c>
       <c r="J7" s="10">
-        <v>0.48626350420726433</v>
+        <v>0.44904057096257244</v>
       </c>
       <c r="K7" s="10">
-        <v>0.21136804796869474</v>
+        <v>0.10031667554957577</v>
       </c>
       <c r="L7" s="10">
-        <v>0.20820201721289638</v>
+        <v>9.9925419634853976E-2</v>
       </c>
       <c r="M7" s="10">
-        <v>7.2908035378282735E-2</v>
+        <v>4.7176958111722504E-2</v>
       </c>
       <c r="N7" s="10">
-        <v>0.25155327849766279</v>
+        <v>0.22739811049598266</v>
       </c>
       <c r="O7" s="10">
-        <v>1.9434211876085121E-2</v>
+        <v>5.2706304312398495E-3</v>
       </c>
       <c r="P7" s="10">
-        <v>0.42678829015377362</v>
+        <v>0.39472657394864147</v>
       </c>
       <c r="Q7" s="10">
-        <v>0.41174186258388196</v>
+        <v>0.3089324198943757</v>
       </c>
       <c r="R7" s="10">
-        <v>0.63862967689083916</v>
+        <v>0.53747476399888505</v>
       </c>
       <c r="S7" s="10">
-        <v>0.34991489758927097</v>
+        <v>0.32611331606864163</v>
       </c>
       <c r="T7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="U7" s="10">
-        <v>0.40712990822690054</v>
+        <v>0.33995213149306697</v>
       </c>
       <c r="V7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="W7" s="10">
-        <v>0.1930850867116003</v>
+        <v>0.2432268389963313</v>
       </c>
       <c r="X7" s="10">
-        <v>0.24660309998065472</v>
+        <v>0.22056378462078183</v>
       </c>
       <c r="Y7" s="10">
-        <v>0.24488959022222861</v>
+        <v>0.24642752491629966</v>
       </c>
       <c r="Z7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AA7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AB7" s="10">
-        <v>1.3485926101053919E-2</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="10">
-        <v>0.6696850181416274</v>
+        <v>0.54367191652224667</v>
       </c>
       <c r="AD7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AE7" s="10">
-        <v>0.2724329340275527</v>
+        <v>0.23603247258696039</v>
       </c>
       <c r="AF7" s="10">
-        <v>0.10004530812973871</v>
+        <v>7.6617749441710944E-2</v>
       </c>
       <c r="AG7" s="10">
-        <v>0.46427191430051906</v>
+        <v>0.44861394264052651</v>
       </c>
       <c r="AH7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AI7" s="10">
-        <v>3.0833949082576476E-2</v>
+        <v>2.0206764163754755E-2</v>
       </c>
       <c r="AJ7" s="10">
-        <v>8.8444610979001484E-2</v>
+        <v>0.16613097499772922</v>
       </c>
       <c r="AK7" s="10">
-        <v>0.49436380693247484</v>
+        <v>0.49821431091519869</v>
       </c>
       <c r="AL7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AM7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AN7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AO7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="AP7" s="10">
-        <v>0.38932817376553347</v>
+        <v>0.32552444729644631</v>
       </c>
       <c r="DG7" s="11"/>
     </row>
@@ -1921,124 +1925,124 @@
         <v>40</v>
       </c>
       <c r="C8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="D8" s="10">
-        <v>3.9449997793473218E-2</v>
+        <v>1.7389698744659527E-2</v>
       </c>
       <c r="E8" s="10">
-        <v>1.2634910320965149E-2</v>
+        <v>1.7158179034191531E-2</v>
       </c>
       <c r="F8" s="10">
-        <v>0.10025885056606097</v>
+        <v>7.5238267290015329E-2</v>
       </c>
       <c r="G8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="H8" s="10">
-        <v>1.6380235085695197E-2</v>
+        <v>1.2523469023981224E-2</v>
       </c>
       <c r="I8" s="10">
-        <v>2.7082360002397315E-2</v>
+        <v>2.6157518920174396E-2</v>
       </c>
       <c r="J8" s="10">
-        <v>0.12605830735068094</v>
+        <v>0.19768770888564538</v>
       </c>
       <c r="K8" s="10">
-        <v>2.6779223815707315E-2</v>
+        <v>2.4165553142070906E-2</v>
       </c>
       <c r="L8" s="10">
-        <v>2.8777032211773801E-2</v>
+        <v>1.9357486955345914E-2</v>
       </c>
       <c r="M8" s="10">
-        <v>9.9320493368516248E-3</v>
+        <v>2.5956398347803675E-3</v>
       </c>
       <c r="N8" s="10">
-        <v>3.3448428492397785E-2</v>
+        <v>3.3229888982334574E-2</v>
       </c>
       <c r="O8" s="10">
-        <v>2.7127636086440855E-2</v>
+        <v>2.5752011421471821E-2</v>
       </c>
       <c r="P8" s="10">
-        <v>2.8247447433782522E-2</v>
+        <v>4.0302599141215575E-2</v>
       </c>
       <c r="Q8" s="10">
-        <v>2.1924327622717499E-2</v>
+        <v>2.5492745924871225E-2</v>
       </c>
       <c r="R8" s="10">
-        <v>1.1286505839263102E-2</v>
+        <v>2.0561312287772551E-2</v>
       </c>
       <c r="S8" s="10">
-        <v>1.6018337533862007E-2</v>
+        <v>1.6039520995745477E-2</v>
       </c>
       <c r="T8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="U8" s="10">
-        <v>6.6085315545221053E-3</v>
+        <v>7.5626856990708459E-3</v>
       </c>
       <c r="V8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="W8" s="10">
-        <v>6.1553365090466952E-2</v>
+        <v>6.6688158575108583E-2</v>
       </c>
       <c r="X8" s="10">
-        <v>3.0752155108550785E-4</v>
+        <v>4.6581218569903706E-4</v>
       </c>
       <c r="Y8" s="10">
-        <v>8.1715390554650921E-2</v>
+        <v>7.489986074028003E-2</v>
       </c>
       <c r="Z8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AA8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AB8" s="10">
         <v>0</v>
       </c>
       <c r="AC8" s="10">
-        <v>3.3131351360693333E-2</v>
+        <v>3.5913861612236427E-2</v>
       </c>
       <c r="AD8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AE8" s="10">
-        <v>3.1273347329682413E-2</v>
+        <v>2.8732617161991759E-2</v>
       </c>
       <c r="AF8" s="10">
-        <v>4.7559984786078226E-3</v>
+        <v>5.2953963983503397E-3</v>
       </c>
       <c r="AG8" s="10">
-        <v>6.8032996034923118E-2</v>
+        <v>4.3628167328786494E-2</v>
       </c>
       <c r="AH8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AI8" s="10">
-        <v>1.1376065697664268E-2</v>
+        <v>8.9739642311337589E-3</v>
       </c>
       <c r="AJ8" s="10">
-        <v>0</v>
+        <v>5.2824774186872474E-2</v>
       </c>
       <c r="AK8" s="10">
-        <v>3.0316299037997294E-2</v>
+        <v>3.5040058743751913E-2</v>
       </c>
       <c r="AL8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AM8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AN8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AO8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="AP8" s="10">
-        <v>4.6574578819737839E-2</v>
+        <v>5.3848781596383226E-2</v>
       </c>
       <c r="DG8" s="11"/>
     </row>
@@ -2050,19 +2054,19 @@
         <v>42</v>
       </c>
       <c r="C9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="D9" s="10">
-        <v>7.4205557123363025E-3</v>
+        <v>6.1110171414925172E-3</v>
       </c>
       <c r="E9" s="10">
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <v>6.2929352726439555E-2</v>
+        <v>6.3298685288545986E-2</v>
       </c>
       <c r="G9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="H9" s="10">
         <v>0</v>
@@ -2071,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="10">
-        <v>4.4902349533992346E-3</v>
+        <v>6.9260838925200297E-3</v>
       </c>
       <c r="K9" s="10">
         <v>0</v>
@@ -2080,34 +2084,34 @@
         <v>0</v>
       </c>
       <c r="M9" s="10">
-        <v>3.4197606485774881E-3</v>
+        <v>7.7044624180364462E-3</v>
       </c>
       <c r="N9" s="10">
-        <v>3.9615900837627061E-5</v>
+        <v>3.7808798716040282E-5</v>
       </c>
       <c r="O9" s="10">
         <v>0</v>
       </c>
       <c r="P9" s="10">
-        <v>1.6097672514683577E-3</v>
+        <v>2.1394539675369749E-3</v>
       </c>
       <c r="Q9" s="10">
-        <v>8.6447992963302571E-3</v>
+        <v>6.4389972099295166E-3</v>
       </c>
       <c r="R9" s="10">
-        <v>2.5684848052661628E-2</v>
+        <v>5.0250479407344617E-2</v>
       </c>
       <c r="S9" s="10">
         <v>0</v>
       </c>
       <c r="T9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="U9" s="10">
-        <v>7.1091598394082169E-3</v>
+        <v>6.4725235337569388E-3</v>
       </c>
       <c r="V9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="W9" s="10">
         <v>0</v>
@@ -2119,10 +2123,10 @@
         <v>0</v>
       </c>
       <c r="Z9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AA9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AB9" s="10">
         <v>0</v>
@@ -2131,43 +2135,43 @@
         <v>0</v>
       </c>
       <c r="AD9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AE9" s="10">
-        <v>1.7527627664560433E-3</v>
+        <v>2.1394265188509564E-3</v>
       </c>
       <c r="AF9" s="10">
-        <v>1.2015320397823815E-3</v>
+        <v>1.4381707548504058E-3</v>
       </c>
       <c r="AG9" s="10">
-        <v>6.2531104057260874E-3</v>
+        <v>6.3391372339896947E-3</v>
       </c>
       <c r="AH9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AI9" s="10">
         <v>0</v>
       </c>
       <c r="AJ9" s="10">
-        <v>4.3129846606946444E-2</v>
+        <v>4.4007226810603157E-2</v>
       </c>
       <c r="AK9" s="10">
         <v>0</v>
       </c>
       <c r="AL9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AM9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AN9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AO9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="AP9" s="10">
-        <v>4.034998767641032E-3</v>
+        <v>4.9143580997735251E-3</v>
       </c>
       <c r="DG9" s="11"/>
     </row>
@@ -2179,34 +2183,34 @@
         <v>44</v>
       </c>
       <c r="C10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="D10" s="10">
-        <v>0.4524527644151658</v>
+        <v>0.43938072178264381</v>
       </c>
       <c r="E10" s="10">
-        <v>2.9955727119292917E-2</v>
+        <v>4.3997050515675755E-2</v>
       </c>
       <c r="F10" s="10">
-        <v>0.1439199769202818</v>
+        <v>0.13345688735838285</v>
       </c>
       <c r="G10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="H10" s="10">
         <v>0</v>
       </c>
       <c r="I10" s="10">
-        <v>0.26887614674824806</v>
+        <v>0.30010445659992874</v>
       </c>
       <c r="J10" s="10">
-        <v>0.12447879812887995</v>
+        <v>0.1596435837556068</v>
       </c>
       <c r="K10" s="10">
-        <v>0.66336379826908165</v>
+        <v>0.71579835248634727</v>
       </c>
       <c r="L10" s="10">
-        <v>0.39228408484674926</v>
+        <v>0.53856319593316337</v>
       </c>
       <c r="M10" s="10">
         <v>0</v>
@@ -2215,88 +2219,88 @@
         <v>0</v>
       </c>
       <c r="O10" s="10">
-        <v>0.57323555616805633</v>
+        <v>0.53639666751485515</v>
       </c>
       <c r="P10" s="10">
-        <v>7.8574345077525462E-2</v>
+        <v>9.0887919901487799E-2</v>
       </c>
       <c r="Q10" s="10">
-        <v>0.14698580659386351</v>
+        <v>0.13600624447762197</v>
       </c>
       <c r="R10" s="10">
-        <v>0.13787316234029526</v>
+        <v>0.13809758071056116</v>
       </c>
       <c r="S10" s="10">
         <v>0</v>
       </c>
       <c r="T10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="U10" s="10">
-        <v>3.2956799590410917E-2</v>
+        <v>2.3710404326605639E-2</v>
       </c>
       <c r="V10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="W10" s="10">
-        <v>0.57378663496424942</v>
+        <v>0.52917739965904165</v>
       </c>
       <c r="X10" s="10">
-        <v>0.35986773612245293</v>
+        <v>0.41858470708222056</v>
       </c>
       <c r="Y10" s="10">
-        <v>0.40748220202700225</v>
+        <v>0.35517063859729281</v>
       </c>
       <c r="Z10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AA10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AB10" s="10">
         <v>0</v>
       </c>
       <c r="AC10" s="10">
-        <v>5.4502011937257427E-2</v>
+        <v>6.5263827517765161E-2</v>
       </c>
       <c r="AD10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AE10" s="10">
-        <v>0.21543494101564525</v>
+        <v>0.22415936675659451</v>
       </c>
       <c r="AF10" s="10">
-        <v>1.9545969484201803E-2</v>
+        <v>8.7817302074712066E-3</v>
       </c>
       <c r="AG10" s="10">
-        <v>0.13537376338840604</v>
+        <v>9.5919634954679853E-2</v>
       </c>
       <c r="AH10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AI10" s="10">
-        <v>0.49947070138223149</v>
+        <v>0.43919642047352675</v>
       </c>
       <c r="AJ10" s="10">
-        <v>0.24924639303087842</v>
+        <v>0.13784759971441063</v>
       </c>
       <c r="AK10" s="10">
-        <v>0.12787368435195964</v>
+        <v>0.21625312714946371</v>
       </c>
       <c r="AL10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AM10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AN10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AO10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="AP10" s="10">
-        <v>0.14520037219225398</v>
+        <v>0.15298096757709151</v>
       </c>
       <c r="DG10" s="11"/>
     </row>
@@ -2308,124 +2312,124 @@
         <v>46</v>
       </c>
       <c r="C11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="D11" s="10">
-        <v>0.14797742585748577</v>
+        <v>0.27562509477954195</v>
       </c>
       <c r="E11" s="10">
-        <v>2.0427181013931109E-2</v>
+        <v>3.3149954807900561E-2</v>
       </c>
       <c r="F11" s="10">
-        <v>0.40894600597103475</v>
+        <v>0.51200605876134553</v>
       </c>
       <c r="G11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="H11" s="10">
-        <v>0.56029932505742819</v>
+        <v>0.49051183917589042</v>
       </c>
       <c r="I11" s="10">
-        <v>2.7637442797953278E-2</v>
+        <v>5.5111528455973613E-2</v>
       </c>
       <c r="J11" s="10">
-        <v>1.4097244076318639E-2</v>
+        <v>2.8692538920918022E-2</v>
       </c>
       <c r="K11" s="10">
-        <v>4.3023738853077143E-2</v>
+        <v>6.0215465325031282E-2</v>
       </c>
       <c r="L11" s="10">
         <v>0</v>
       </c>
       <c r="M11" s="10">
-        <v>0.76168299238205639</v>
+        <v>0.73807383669273208</v>
       </c>
       <c r="N11" s="10">
-        <v>0.42655811253788711</v>
+        <v>0.51665470856556706</v>
       </c>
       <c r="O11" s="10">
-        <v>6.7281588287103303E-2</v>
+        <v>8.5824188150072686E-2</v>
       </c>
       <c r="P11" s="10">
-        <v>6.4620716861921085E-2</v>
+        <v>4.6004532838202411E-2</v>
       </c>
       <c r="Q11" s="10">
         <v>0</v>
       </c>
       <c r="R11" s="10">
-        <v>5.1269348705014631E-3</v>
+        <v>5.1638842604697692E-2</v>
       </c>
       <c r="S11" s="10">
-        <v>5.1189354856479199E-2</v>
+        <v>5.4201606466584909E-2</v>
       </c>
       <c r="T11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="U11" s="10">
-        <v>0.31147992550194231</v>
+        <v>0.31497859116409471</v>
       </c>
       <c r="V11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="W11" s="10">
-        <v>1.9147996911159898E-2</v>
+        <v>3.1258790387375945E-2</v>
       </c>
       <c r="X11" s="10">
         <v>0</v>
       </c>
       <c r="Y11" s="10">
-        <v>3.5106154554940538E-3</v>
+        <v>4.0452513604819296E-3</v>
       </c>
       <c r="Z11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AA11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AB11" s="10">
-        <v>0.23967592703041346</v>
+        <v>0.25178355706416283</v>
       </c>
       <c r="AC11" s="10">
-        <v>9.3835729692635372E-2</v>
+        <v>0.13310410509959109</v>
       </c>
       <c r="AD11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AE11" s="10">
-        <v>1.0362664324368515E-2</v>
+        <v>1.2661280215902869E-2</v>
       </c>
       <c r="AF11" s="10">
-        <v>0.7679137734344279</v>
+        <v>0.72186726802274648</v>
       </c>
       <c r="AG11" s="10">
-        <v>0</v>
+        <v>0.10961981603912424</v>
       </c>
       <c r="AH11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AI11" s="10">
-        <v>0.12872254400817645</v>
+        <v>0.11503177288587285</v>
       </c>
       <c r="AJ11" s="10">
-        <v>0</v>
+        <v>4.2431557220789111E-2</v>
       </c>
       <c r="AK11" s="10">
-        <v>3.5212951948571797E-2</v>
+        <v>6.7240908671701752E-2</v>
       </c>
       <c r="AL11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AM11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AN11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AO11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="AP11" s="10">
-        <v>0.12497967123142001</v>
+        <v>0.16115588025601574</v>
       </c>
       <c r="DG11" s="11"/>
     </row>
@@ -2437,124 +2441,124 @@
         <v>48</v>
       </c>
       <c r="C12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="D12" s="10">
-        <v>7.2016220098029674E-2</v>
+        <v>7.3290568488357813E-2</v>
       </c>
       <c r="E12" s="10">
-        <v>0.1234944455761722</v>
+        <v>0.17172059965490258</v>
       </c>
       <c r="F12" s="10">
-        <v>0.16056319546735504</v>
+        <v>0.10106800321864839</v>
       </c>
       <c r="G12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="H12" s="10">
-        <v>0.25771401206710692</v>
+        <v>0.33770673178600213</v>
       </c>
       <c r="I12" s="10">
-        <v>0.24506276954374465</v>
+        <v>0.20633655762843792</v>
       </c>
       <c r="J12" s="10">
-        <v>3.274773180912189E-2</v>
+        <v>5.1200659057713642E-3</v>
       </c>
       <c r="K12" s="10">
-        <v>2.9383052781420574E-2</v>
+        <v>1.037323889875157E-3</v>
       </c>
       <c r="L12" s="10">
-        <v>0.31136086621887643</v>
+        <v>0.2401233083592958</v>
       </c>
       <c r="M12" s="10">
-        <v>0.10489717835990306</v>
+        <v>0.1474407483023947</v>
       </c>
       <c r="N12" s="10">
-        <v>2.6065525817511467E-2</v>
+        <v>1.9415471215161139E-2</v>
       </c>
       <c r="O12" s="10">
-        <v>0.19211558277144222</v>
+        <v>0.22465752329654073</v>
       </c>
       <c r="P12" s="10">
-        <v>0.23570117232836746</v>
+        <v>0.22479034153646063</v>
       </c>
       <c r="Q12" s="10">
-        <v>0.3703254019351625</v>
+        <v>0.47226774863178311</v>
       </c>
       <c r="R12" s="10">
-        <v>0.14148459340281846</v>
+        <v>0.16207550624348199</v>
       </c>
       <c r="S12" s="10">
-        <v>0.45572673241473194</v>
+        <v>0.47843542665253774</v>
       </c>
       <c r="T12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="U12" s="10">
-        <v>0.17290506096421662</v>
+        <v>0.24284156159347675</v>
       </c>
       <c r="V12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="W12" s="10">
-        <v>6.1110181593820048E-2</v>
+        <v>4.2133961105561633E-2</v>
       </c>
       <c r="X12" s="10">
-        <v>0.17438450948067968</v>
+        <v>0.13031848343206012</v>
       </c>
       <c r="Y12" s="10">
-        <v>0.1276269442288977</v>
+        <v>0.14098630389653097</v>
       </c>
       <c r="Z12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AA12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AB12" s="10">
-        <v>0.49611995531986552</v>
+        <v>0.54747391912878351</v>
       </c>
       <c r="AC12" s="10">
-        <v>8.3369709132708456E-2</v>
+        <v>0.12448146809732953</v>
       </c>
       <c r="AD12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AE12" s="10">
-        <v>0.27940662500939667</v>
+        <v>0.38834991877765024</v>
       </c>
       <c r="AF12" s="10">
-        <v>7.2462613976445309E-2</v>
+        <v>0.16492949593295098</v>
       </c>
       <c r="AG12" s="10">
-        <v>6.6791802266282924E-3</v>
+        <v>2.7020556530145838E-2</v>
       </c>
       <c r="AH12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AI12" s="1">
-        <v>970.79883437148453</v>
+        <v>0.36541194961890283</v>
       </c>
       <c r="AJ12" s="1">
-        <v>970.79883437148453</v>
+        <v>0.30497589413541509</v>
       </c>
       <c r="AK12" s="1">
-        <v>970.79883437148453</v>
+        <v>0.11499485853808088</v>
       </c>
       <c r="AL12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AM12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AN12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AO12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="AP12" s="10">
-        <v>0.14847420484978488</v>
+        <v>0.17856643780435544</v>
       </c>
       <c r="DG12" s="12"/>
     </row>
@@ -2566,10 +2570,10 @@
         <v>50</v>
       </c>
       <c r="C13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="D13" s="10">
-        <v>0</v>
+        <v>1.0503912229146736E-3</v>
       </c>
       <c r="E13" s="10">
         <v>0</v>
@@ -2578,16 +2582,16 @@
         <v>0</v>
       </c>
       <c r="G13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="H13" s="10">
-        <v>0</v>
+        <v>1.9309597685268111E-3</v>
       </c>
       <c r="I13" s="10">
         <v>0</v>
       </c>
       <c r="J13" s="10">
-        <v>0</v>
+        <v>1.0670685948864301E-3</v>
       </c>
       <c r="K13" s="10">
         <v>0</v>
@@ -2599,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="N13" s="10">
-        <v>0</v>
+        <v>7.9146409921398682E-5</v>
       </c>
       <c r="O13" s="10">
-        <v>0</v>
+        <v>4.3030969689073495E-3</v>
       </c>
       <c r="P13" s="10">
-        <v>0</v>
+        <v>3.1361695357430323E-3</v>
       </c>
       <c r="Q13" s="10">
         <v>0</v>
@@ -2617,13 +2621,13 @@
         <v>0</v>
       </c>
       <c r="T13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="U13" s="10">
-        <v>0</v>
+        <v>1.1801338435060908E-5</v>
       </c>
       <c r="V13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="W13" s="10">
         <v>0</v>
@@ -2635,34 +2639,34 @@
         <v>0</v>
       </c>
       <c r="Z13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AA13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AB13" s="10">
         <v>0</v>
       </c>
       <c r="AC13" s="10">
-        <v>0</v>
+        <v>1.5487748721214776E-3</v>
       </c>
       <c r="AD13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AE13" s="10">
-        <v>0</v>
+        <v>1.7910917283127666E-5</v>
       </c>
       <c r="AF13" s="10">
-        <v>0</v>
+        <v>2.003863265482697E-4</v>
       </c>
       <c r="AG13" s="10">
         <v>0</v>
       </c>
       <c r="AH13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AI13" s="10">
-        <v>0</v>
+        <v>1.3056721036756943E-2</v>
       </c>
       <c r="AJ13" s="10">
         <v>0</v>
@@ -2671,19 +2675,19 @@
         <v>0</v>
       </c>
       <c r="AL13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AM13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AN13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AO13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="AP13" s="10">
-        <v>0</v>
+        <v>1.4636380541851652E-3</v>
       </c>
       <c r="DG13" s="12"/>
     </row>
@@ -2695,124 +2699,124 @@
         <v>52</v>
       </c>
       <c r="C14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="D14" s="10">
-        <v>0</v>
+        <v>2.4978069182509852E-4</v>
       </c>
       <c r="E14" s="10">
-        <v>0</v>
+        <v>1.2287427423084711E-2</v>
       </c>
       <c r="F14" s="10">
-        <v>0</v>
+        <v>2.6299899882653854E-3</v>
       </c>
       <c r="G14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="H14" s="10">
-        <v>0</v>
+        <v>6.8015352949430813E-3</v>
       </c>
       <c r="I14" s="10">
-        <v>0</v>
+        <v>1.0101588743831977E-2</v>
       </c>
       <c r="J14" s="10">
-        <v>0</v>
+        <v>2.3106860357879962E-2</v>
       </c>
       <c r="K14" s="10">
-        <v>0</v>
+        <v>6.4677666880467805E-2</v>
       </c>
       <c r="L14" s="10">
-        <v>0</v>
+        <v>1.0330199706099703E-2</v>
       </c>
       <c r="M14" s="10">
-        <v>0</v>
+        <v>5.185524659813724E-3</v>
       </c>
       <c r="N14" s="10">
-        <v>0</v>
+        <v>7.7805607096937878E-3</v>
       </c>
       <c r="O14" s="10">
-        <v>0</v>
+        <v>6.9670951052889073E-3</v>
       </c>
       <c r="P14" s="10">
-        <v>0</v>
+        <v>2.0930735346182585E-2</v>
       </c>
       <c r="Q14" s="10">
-        <v>0</v>
+        <v>8.8113113492593366E-4</v>
       </c>
       <c r="R14" s="10">
-        <v>0</v>
+        <v>3.07550434241336E-3</v>
       </c>
       <c r="S14" s="10">
-        <v>0</v>
+        <v>7.0210280912239723E-3</v>
       </c>
       <c r="T14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="U14" s="10">
-        <v>0</v>
+        <v>2.8475154338743584E-3</v>
       </c>
       <c r="V14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="W14" s="10">
-        <v>0</v>
+        <v>1.6245364073929472E-2</v>
       </c>
       <c r="X14" s="10">
-        <v>0</v>
+        <v>3.6353556870037038E-3</v>
       </c>
       <c r="Y14" s="10">
-        <v>0</v>
+        <v>6.5871168994665E-3</v>
       </c>
       <c r="Z14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AA14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AB14" s="10">
-        <v>0</v>
+        <v>1.8733706093160548E-2</v>
       </c>
       <c r="AC14" s="10">
-        <v>0</v>
+        <v>1.4199713850793277E-2</v>
       </c>
       <c r="AD14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AE14" s="10">
-        <v>0</v>
+        <v>1.1777710535079741E-2</v>
       </c>
       <c r="AF14" s="10">
-        <v>0</v>
+        <v>1.0051725989865125E-4</v>
       </c>
       <c r="AG14" s="10">
-        <v>0</v>
+        <v>1.2942534816356166E-3</v>
       </c>
       <c r="AH14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AI14" s="10">
-        <v>0</v>
+        <v>1.2089677348918095E-3</v>
       </c>
       <c r="AJ14" s="10">
-        <v>0</v>
+        <v>7.9416123049183638E-3</v>
       </c>
       <c r="AK14" s="10">
-        <v>0</v>
+        <v>8.7148287680703478E-3</v>
       </c>
       <c r="AL14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AM14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AN14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AO14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="AP14" s="10">
-        <v>0</v>
+        <v>1.2360516717406738E-2</v>
       </c>
       <c r="DG14" s="12"/>
     </row>
@@ -2953,124 +2957,124 @@
         <v>55</v>
       </c>
       <c r="C16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="D16" s="10">
-        <v>6.4218289500136702E-3</v>
+        <v>4.7548550078492713E-3</v>
       </c>
       <c r="E16" s="10">
-        <v>1.2916686446999486E-2</v>
+        <v>1.1782892163285775E-2</v>
       </c>
       <c r="F16" s="10">
-        <v>3.4945429844752017E-3</v>
+        <v>3.1367540398529979E-3</v>
       </c>
       <c r="G16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="H16" s="10">
-        <v>2.7161875090354472E-3</v>
+        <v>2.6599617194824707E-3</v>
       </c>
       <c r="I16" s="10">
-        <v>7.8629926645787957E-3</v>
+        <v>7.7384145170966423E-3</v>
       </c>
       <c r="J16" s="10">
-        <v>1.236176345251094E-2</v>
+        <v>1.1541371456323207E-2</v>
       </c>
       <c r="K16" s="10">
-        <v>6.5049365878461765E-3</v>
+        <v>5.9739662075798594E-3</v>
       </c>
       <c r="L16" s="10">
-        <v>5.9145747088695123E-3</v>
+        <v>5.4021198085612617E-3</v>
       </c>
       <c r="M16" s="10">
-        <v>1.7095072523688399E-3</v>
+        <v>1.2968687971950566E-3</v>
       </c>
       <c r="N16" s="10">
-        <v>8.0696676487308945E-3</v>
+        <v>6.6482788960772468E-3</v>
       </c>
       <c r="O16" s="10">
-        <v>4.6088855428330832E-3</v>
+        <v>4.264998856695023E-3</v>
       </c>
       <c r="P16" s="10">
-        <v>9.5941796313348433E-3</v>
+        <v>9.8875622904869703E-3</v>
       </c>
       <c r="Q16" s="10">
-        <v>7.8320662432654828E-3</v>
+        <v>6.3836242778996443E-3</v>
       </c>
       <c r="R16" s="10">
-        <v>1.1365624248512641E-2</v>
+        <v>9.9263085910539298E-3</v>
       </c>
       <c r="S16" s="10">
-        <v>7.5721337390774641E-3</v>
+        <v>7.1623050302622639E-3</v>
       </c>
       <c r="T16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="U16" s="10">
-        <v>7.2687132049430786E-3</v>
+        <v>6.2376600157756697E-3</v>
       </c>
       <c r="V16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="W16" s="10">
-        <v>6.5492230355517957E-3</v>
+        <v>7.3292177440830051E-3</v>
       </c>
       <c r="X16" s="10">
-        <v>8.7044288889632157E-3</v>
+        <v>8.6882465893693417E-3</v>
       </c>
       <c r="Y16" s="10">
-        <v>8.1148036922261343E-3</v>
+        <v>8.5628447231620754E-3</v>
       </c>
       <c r="Z16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AA16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AB16" s="10">
-        <v>4.1246749950811911E-3</v>
+        <v>3.1386351379486255E-3</v>
       </c>
       <c r="AC16" s="10">
-        <v>1.1979630905673E-2</v>
+        <v>1.0478005249192568E-2</v>
       </c>
       <c r="AD16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AE16" s="10">
-        <v>7.4092824963037929E-3</v>
+        <v>6.0930795575995485E-3</v>
       </c>
       <c r="AF16" s="10">
-        <v>2.1727442539434009E-3</v>
+        <v>1.5622189344589609E-3</v>
       </c>
       <c r="AG16" s="10">
-        <v>1.3328568770394809E-2</v>
+        <v>1.1962175307542336E-2</v>
       </c>
       <c r="AH16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AI16" s="10">
-        <v>3.6575155543183829E-3</v>
+        <v>2.8934370795541094E-3</v>
       </c>
       <c r="AJ16" s="10">
-        <v>5.2787741486732152E-3</v>
+        <v>7.6565352112914747E-3</v>
       </c>
       <c r="AK16" s="10">
-        <v>9.1733982424292097E-3</v>
+        <v>9.6033263735321745E-3</v>
       </c>
       <c r="AL16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AM16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AN16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AO16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="AP16" s="10">
-        <v>9.0732754187459411E-3</v>
+        <v>7.9051621002147205E-3</v>
       </c>
       <c r="DG16" s="14"/>
     </row>
@@ -3082,124 +3086,124 @@
         <v>56</v>
       </c>
       <c r="C17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="D17" s="15">
-        <v>0.2244142381226919</v>
+        <v>0.24390144172304556</v>
       </c>
       <c r="E17" s="15">
-        <v>0.43194333632317955</v>
+        <v>0.46744433433709243</v>
       </c>
       <c r="F17" s="15">
-        <v>0.30132902019162505</v>
+        <v>0.3464628189532577</v>
       </c>
       <c r="G17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="H17" s="15">
-        <v>0.70499526887421415</v>
+        <v>0.77119454047046165</v>
       </c>
       <c r="I17" s="15">
-        <v>0.21201072355993372</v>
+        <v>0.22560595740491332</v>
       </c>
       <c r="J17" s="15">
-        <v>0.20482097827235571</v>
+        <v>0.23226931245448387</v>
       </c>
       <c r="K17" s="15">
-        <v>0.30613407594215769</v>
+        <v>0.37719470588037785</v>
       </c>
       <c r="L17" s="15">
-        <v>7.9797175183227431E-2</v>
+        <v>9.3565849752905147E-2</v>
       </c>
       <c r="M17" s="15">
-        <v>0.62179389403612439</v>
+        <v>0.66796944619054022</v>
       </c>
       <c r="N17" s="15">
-        <v>0.59115223438288511</v>
+        <v>0.6284587500224994</v>
       </c>
       <c r="O17" s="15">
-        <v>0.23628725108355758</v>
+        <v>0.26036041128058823</v>
       </c>
       <c r="P17" s="15">
-        <v>0.54761210755515988</v>
+        <v>0.61713347285659792</v>
       </c>
       <c r="Q17" s="15">
-        <v>0.44448219947876172</v>
+        <v>0.46975465391475235</v>
       </c>
       <c r="R17" s="15">
-        <v>0.27601611880709892</v>
+        <v>0.30755979097715114</v>
       </c>
       <c r="S17" s="15">
-        <v>0.36602945632124656</v>
+        <v>0.41922776358062097</v>
       </c>
       <c r="T17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="U17" s="15">
-        <v>0.50002359761303228</v>
+        <v>0.54664979137143077</v>
       </c>
       <c r="V17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="W17" s="15">
-        <v>0.11131152154302286</v>
+        <v>0.12674638692814238</v>
       </c>
       <c r="X17" s="15">
-        <v>0.49118604828938184</v>
+        <v>0.54122700248944444</v>
       </c>
       <c r="Y17" s="15">
-        <v>0.13483388888169751</v>
+        <v>0.15140826983375272</v>
       </c>
       <c r="Z17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AA17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AB17" s="15">
-        <v>0.73288927217076494</v>
+        <v>0.83013731942662727</v>
       </c>
       <c r="AC17" s="15">
-        <v>0.3919214674698403</v>
+        <v>0.43295297235784819</v>
       </c>
       <c r="AD17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AE17" s="15">
-        <v>0.1367501363922026</v>
+        <v>0.14617887680746108</v>
       </c>
       <c r="AF17" s="15">
-        <v>0.52907033435160289</v>
+        <v>0.5964563967868366</v>
       </c>
       <c r="AG17" s="15">
-        <v>0.14356091012132918</v>
+        <v>0.15945081196429206</v>
       </c>
       <c r="AH17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AI17" s="15">
-        <v>0.31917369057934658</v>
+        <v>0.33784568656893554</v>
       </c>
       <c r="AJ17" s="15">
-        <v>0.31406719731746208</v>
+        <v>0.3369514683664781</v>
       </c>
       <c r="AK17" s="15">
-        <v>0.20987551509787392</v>
+        <v>0.23645691087263881</v>
       </c>
       <c r="AL17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AM17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AN17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AO17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="AP17" s="15">
-        <v>0.37016733475089147</v>
+        <v>0.40659032466655992</v>
       </c>
       <c r="DG17" s="8"/>
     </row>
@@ -3211,100 +3215,100 @@
         <v>36</v>
       </c>
       <c r="C18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="D18" s="10">
-        <v>8.4820746059039477E-3</v>
+        <v>8.7196648189182373E-3</v>
       </c>
       <c r="E18" s="10">
-        <v>7.8692366605379073E-3</v>
+        <v>8.1499064973284078E-3</v>
       </c>
       <c r="F18" s="10">
         <v>0</v>
       </c>
       <c r="G18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="H18" s="10">
         <v>0</v>
       </c>
       <c r="I18" s="10">
-        <v>6.9634911518574542E-3</v>
+        <v>6.9495330334109666E-3</v>
       </c>
       <c r="J18" s="10">
-        <v>5.8829022643347838E-3</v>
+        <v>6.6862872585516158E-3</v>
       </c>
       <c r="K18" s="10">
-        <v>5.405162454719321E-3</v>
+        <v>5.2647865739875446E-3</v>
       </c>
       <c r="L18" s="10">
         <v>0</v>
       </c>
       <c r="M18" s="10">
-        <v>2.9161867339236713E-2</v>
+        <v>2.9694108064170482E-2</v>
       </c>
       <c r="N18" s="10">
-        <v>5.752347662017189E-3</v>
+        <v>6.1835340782702012E-3</v>
       </c>
       <c r="O18" s="10">
         <v>0</v>
       </c>
       <c r="P18" s="10">
-        <v>4.1538988723191624E-2</v>
+        <v>4.5851719826791724E-2</v>
       </c>
       <c r="Q18" s="10">
-        <v>6.2132447378953478E-3</v>
+        <v>9.47310196937938E-3</v>
       </c>
       <c r="R18" s="10">
-        <v>9.7637297570612683E-3</v>
+        <v>1.0424640071421049E-2</v>
       </c>
       <c r="S18" s="10">
-        <v>1.4661668654729065E-2</v>
+        <v>1.5486697409466918E-2</v>
       </c>
       <c r="T18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="U18" s="10">
-        <v>1.5584940707998252E-2</v>
+        <v>1.8427131851015483E-2</v>
       </c>
       <c r="V18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="W18" s="10">
         <v>0</v>
       </c>
       <c r="X18" s="10">
-        <v>4.2589128205963826E-2</v>
+        <v>3.6046692546594199E-2</v>
       </c>
       <c r="Y18" s="10">
         <v>0</v>
       </c>
       <c r="Z18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AA18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AB18" s="10">
         <v>0</v>
       </c>
       <c r="AC18" s="10">
-        <v>3.2419554304218293E-2</v>
+        <v>2.6119872569640962E-2</v>
       </c>
       <c r="AD18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AE18" s="20">
-        <v>1.1018287895728625E-2</v>
+        <v>1.1451361464688553E-2</v>
       </c>
       <c r="AF18" s="20">
-        <v>1.4255163985775357E-2</v>
+        <v>1.4335184692684135E-2</v>
       </c>
       <c r="AG18" s="20">
         <v>0</v>
       </c>
       <c r="AH18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AI18" s="20">
         <v>0</v>
@@ -3313,22 +3317,22 @@
         <v>0</v>
       </c>
       <c r="AK18" s="20">
-        <v>2.075253687361461E-2</v>
+        <v>2.1280946128824977E-2</v>
       </c>
       <c r="AL18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AM18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AN18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AO18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="AP18" s="10">
-        <v>1.4777483315545546E-2</v>
+        <v>1.6211843909598071E-2</v>
       </c>
       <c r="DG18" s="11"/>
     </row>
@@ -3340,100 +3344,100 @@
         <v>59</v>
       </c>
       <c r="C19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="D19" s="10">
-        <v>0.991517925394096</v>
+        <v>0.99128033518108183</v>
       </c>
       <c r="E19" s="10">
-        <v>0.99213076333946215</v>
+        <v>0.99185009350267161</v>
       </c>
       <c r="F19" s="10">
         <v>1</v>
       </c>
       <c r="G19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
       </c>
       <c r="I19" s="10">
-        <v>0.99303650884814287</v>
+        <v>0.9930504669665895</v>
       </c>
       <c r="J19" s="10">
-        <v>0.99411709773566526</v>
+        <v>0.99331371274144853</v>
       </c>
       <c r="K19" s="10">
-        <v>0.99459483754528022</v>
+        <v>0.99473521342601245</v>
       </c>
       <c r="L19" s="10">
         <v>1</v>
       </c>
       <c r="M19" s="10">
-        <v>0.97083813266076313</v>
+        <v>0.9703058919358295</v>
       </c>
       <c r="N19" s="10">
-        <v>0.99424765233798307</v>
+        <v>0.99381646592172979</v>
       </c>
       <c r="O19" s="10">
         <v>1</v>
       </c>
       <c r="P19" s="10">
-        <v>0.95846101127680838</v>
+        <v>0.95414828017320819</v>
       </c>
       <c r="Q19" s="10">
-        <v>0.99378675526210469</v>
+        <v>0.99052689803062066</v>
       </c>
       <c r="R19" s="10">
-        <v>0.99023627024293881</v>
+        <v>0.98957535992857903</v>
       </c>
       <c r="S19" s="10">
-        <v>0.98533833134527105</v>
+        <v>0.98451330259053338</v>
       </c>
       <c r="T19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="U19" s="10">
-        <v>0.98441505929200168</v>
+        <v>0.98157286814898426</v>
       </c>
       <c r="V19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="W19" s="10">
         <v>1</v>
       </c>
       <c r="X19" s="10">
-        <v>0.95741087179403594</v>
+        <v>0.96395330745340602</v>
       </c>
       <c r="Y19" s="10">
         <v>1</v>
       </c>
       <c r="Z19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AA19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AB19" s="10">
         <v>1</v>
       </c>
       <c r="AC19" s="10">
-        <v>0.96758044569578161</v>
+        <v>0.97388012743035923</v>
       </c>
       <c r="AD19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AE19" s="20">
-        <v>0.98898171210427088</v>
+        <v>0.98854863853531205</v>
       </c>
       <c r="AF19" s="20">
-        <v>0.98574483601422469</v>
+        <v>0.98566481530731598</v>
       </c>
       <c r="AG19" s="20">
         <v>1</v>
       </c>
       <c r="AH19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AI19" s="20">
         <v>1</v>
@@ -3442,22 +3446,22 @@
         <v>1</v>
       </c>
       <c r="AK19" s="20">
-        <v>0.97924746312638533</v>
+        <v>0.97871905387117497</v>
       </c>
       <c r="AL19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AM19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AN19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AO19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="AP19" s="10">
-        <v>0.98522251668445449</v>
+        <v>0.98378815609040138</v>
       </c>
       <c r="DG19" s="11"/>
     </row>
@@ -3598,7 +3602,7 @@
         <v>30</v>
       </c>
       <c r="C21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="D21" s="10">
         <v>0</v>
@@ -3610,7 +3614,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="H21" s="10">
         <v>0</v>
@@ -3649,13 +3653,13 @@
         <v>0</v>
       </c>
       <c r="T21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="U21" s="10">
         <v>0</v>
       </c>
       <c r="V21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="W21" s="10">
         <v>0</v>
@@ -3667,10 +3671,10 @@
         <v>0</v>
       </c>
       <c r="Z21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AA21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AB21" s="10">
         <v>0</v>
@@ -3679,10 +3683,10 @@
         <v>0</v>
       </c>
       <c r="AD21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AE21" s="20">
-        <v>3.7749888045196162E-2</v>
+        <v>1.2512338239162688E-2</v>
       </c>
       <c r="AF21" s="20">
         <v>0</v>
@@ -3691,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="AH21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AI21" s="20">
         <v>0</v>
@@ -3700,22 +3704,22 @@
         <v>0</v>
       </c>
       <c r="AK21" s="20">
-        <v>3.7833303928805351E-2</v>
+        <v>1.6056674316481421E-2</v>
       </c>
       <c r="AL21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AM21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AN21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AO21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="AP21" s="10">
-        <v>2.92455447401185E-3</v>
+        <v>1.0157059032981136E-3</v>
       </c>
       <c r="DG21" s="11"/>
     </row>
@@ -3727,28 +3731,28 @@
         <v>32</v>
       </c>
       <c r="C22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="D22" s="10">
         <v>0</v>
       </c>
       <c r="E22" s="10">
-        <v>1.0563002205832955E-2</v>
+        <v>1.3550919471992754E-2</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="H22" s="10">
-        <v>0.15479999170221706</v>
+        <v>0.17649547705699203</v>
       </c>
       <c r="I22" s="10">
         <v>0</v>
       </c>
       <c r="J22" s="10">
-        <v>5.6350780028414007E-3</v>
+        <v>3.8175382624950527E-3</v>
       </c>
       <c r="K22" s="10">
         <v>0</v>
@@ -3757,19 +3761,19 @@
         <v>0</v>
       </c>
       <c r="M22" s="10">
-        <v>3.4237778754238953E-2</v>
+        <v>4.6603596893614624E-2</v>
       </c>
       <c r="N22" s="10">
-        <v>2.22048150222545E-2</v>
+        <v>4.6716068936649965E-2</v>
       </c>
       <c r="O22" s="10">
         <v>0</v>
       </c>
       <c r="P22" s="10">
-        <v>1.3813640580764047E-2</v>
+        <v>8.688282207970778E-3</v>
       </c>
       <c r="Q22" s="10">
-        <v>3.3601164984218147E-2</v>
+        <v>2.4821660379176765E-2</v>
       </c>
       <c r="R22" s="10">
         <v>0</v>
@@ -3778,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="T22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="U22" s="10">
-        <v>1.6687901445317909E-2</v>
+        <v>1.4976611103695563E-2</v>
       </c>
       <c r="V22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="W22" s="10">
         <v>0</v>
@@ -3796,55 +3800,55 @@
         <v>0</v>
       </c>
       <c r="Z22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AA22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AB22" s="10">
-        <v>1.8465649532651777E-2</v>
+        <v>1.5248149951539813E-2</v>
       </c>
       <c r="AC22" s="10">
         <v>0</v>
       </c>
       <c r="AD22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AE22" s="20">
-        <v>3.1741334522769157E-2</v>
+        <v>2.2661369967244289E-2</v>
       </c>
       <c r="AF22" s="20">
-        <v>3.8759480105883322E-2</v>
+        <v>3.6077171278908492E-2</v>
       </c>
       <c r="AG22" s="20">
         <v>0</v>
       </c>
       <c r="AH22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AI22" s="20">
         <v>0</v>
       </c>
       <c r="AJ22" s="20">
-        <v>0.1295610627079517</v>
+        <v>7.2132504698819155E-2</v>
       </c>
       <c r="AK22" s="20">
         <v>0</v>
       </c>
       <c r="AL22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AM22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AN22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AO22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="AP22" s="10">
-        <v>1.2327117192137549E-2</v>
+        <v>1.2498567840860357E-2</v>
       </c>
       <c r="DG22" s="11"/>
     </row>
@@ -3856,124 +3860,124 @@
         <v>34</v>
       </c>
       <c r="C23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="D23" s="10">
-        <v>6.3678484110607642E-2</v>
+        <v>6.7023519959216613E-2</v>
       </c>
       <c r="E23" s="10">
-        <v>0.16363788346347535</v>
+        <v>0.15557880623266668</v>
       </c>
       <c r="F23" s="10">
-        <v>7.8960328512660185E-3</v>
+        <v>1.8020781941847943E-2</v>
       </c>
       <c r="G23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="H23" s="10">
-        <v>2.9961907838197067E-2</v>
+        <v>3.1799690630253702E-2</v>
       </c>
       <c r="I23" s="10">
         <v>0</v>
       </c>
       <c r="J23" s="10">
-        <v>0.13089299489710593</v>
+        <v>0.10493306849633613</v>
       </c>
       <c r="K23" s="10">
-        <v>9.0294785778950361E-3</v>
+        <v>1.1066258455010457E-2</v>
       </c>
       <c r="L23" s="10">
-        <v>3.84224240149727E-2</v>
+        <v>4.2959000940158018E-2</v>
       </c>
       <c r="M23" s="10">
-        <v>1.6961348622150825E-2</v>
+        <v>1.4693094412317888E-2</v>
       </c>
       <c r="N23" s="10">
-        <v>0.28180958368917847</v>
+        <v>0.27398571438796565</v>
       </c>
       <c r="O23" s="10">
-        <v>6.213956988027175E-2</v>
+        <v>4.0125718282979887E-2</v>
       </c>
       <c r="P23" s="10">
-        <v>0.10558566323215214</v>
+        <v>0.10155844597718013</v>
       </c>
       <c r="Q23" s="10">
-        <v>7.321686896249073E-2</v>
+        <v>4.8664125225487471E-2</v>
       </c>
       <c r="R23" s="10">
         <v>0</v>
       </c>
       <c r="S23" s="10">
-        <v>0.10609701994707389</v>
+        <v>0.11391197714480737</v>
       </c>
       <c r="T23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="U23" s="10">
-        <v>1.235815527018598E-2</v>
+        <v>1.2006195410653018E-2</v>
       </c>
       <c r="V23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="W23" s="10">
-        <v>7.1843409889404772E-3</v>
+        <v>3.7523715327059848E-3</v>
       </c>
       <c r="X23" s="10">
-        <v>0.2363439870127903</v>
+        <v>0.15569747290445182</v>
       </c>
       <c r="Y23" s="10">
-        <v>5.1915127747669092E-2</v>
+        <v>4.5837268638914276E-2</v>
       </c>
       <c r="Z23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AA23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AB23" s="10">
         <v>0</v>
       </c>
       <c r="AC23" s="10">
-        <v>4.2434125624873288E-2</v>
+        <v>4.2397805984726471E-2</v>
       </c>
       <c r="AD23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AE23" s="20">
-        <v>4.0804818307382397E-2</v>
+        <v>3.6935142993790145E-2</v>
       </c>
       <c r="AF23" s="20">
-        <v>0.18435412095196133</v>
+        <v>0.17132656588023043</v>
       </c>
       <c r="AG23" s="20">
-        <v>0.24235217903970144</v>
+        <v>0.22637205282728257</v>
       </c>
       <c r="AH23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AI23" s="20">
-        <v>7.4720672150021608E-2</v>
+        <v>3.3476221510113167E-2</v>
       </c>
       <c r="AJ23" s="20">
-        <v>0.16227050493112644</v>
+        <v>0.16074734541624622</v>
       </c>
       <c r="AK23" s="20">
         <v>0</v>
       </c>
       <c r="AL23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AM23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AN23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AO23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="AP23" s="10">
-        <v>0.10031944776538876</v>
+        <v>8.7222299237271109E-2</v>
       </c>
       <c r="DG23" s="11"/>
     </row>
@@ -3985,124 +3989,124 @@
         <v>38</v>
       </c>
       <c r="C24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="D24" s="10">
-        <v>9.7306893840187217E-2</v>
+        <v>0.11836366487017193</v>
       </c>
       <c r="E24" s="10">
-        <v>0.55935974744541095</v>
+        <v>0.38002709937936308</v>
       </c>
       <c r="F24" s="10">
-        <v>0.13177755887050613</v>
+        <v>0.11917731561369062</v>
       </c>
       <c r="G24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="H24" s="10">
         <v>0</v>
       </c>
       <c r="I24" s="10">
-        <v>0.4338603410880279</v>
+        <v>0.33866591227839149</v>
       </c>
       <c r="J24" s="10">
-        <v>0.61503600831278959</v>
+        <v>0.72120189399242651</v>
       </c>
       <c r="K24" s="10">
-        <v>0.12714596485013624</v>
+        <v>5.2223355385199732E-2</v>
       </c>
       <c r="L24" s="10">
-        <v>0.21212189581316671</v>
+        <v>0.10770807090114774</v>
       </c>
       <c r="M24" s="10">
-        <v>8.9907169161299497E-2</v>
+        <v>2.8949573113311543E-2</v>
       </c>
       <c r="N24" s="10">
-        <v>0.33266945082191912</v>
+        <v>0.3455843042420832</v>
       </c>
       <c r="O24" s="10">
-        <v>1.1310080652595172E-2</v>
+        <v>2.5969184259173952E-3</v>
       </c>
       <c r="P24" s="10">
-        <v>0.19545589368541727</v>
+        <v>0.17160936953019415</v>
       </c>
       <c r="Q24" s="10">
-        <v>0.41565139022158637</v>
+        <v>0.31260583317108093</v>
       </c>
       <c r="R24" s="10">
-        <v>0.61278481246867134</v>
+        <v>0.55590735774669486</v>
       </c>
       <c r="S24" s="10">
-        <v>0.21578860103320394</v>
+        <v>0.22633497254493104</v>
       </c>
       <c r="T24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="U24" s="10">
-        <v>0.46864868240209789</v>
+        <v>0.39144147794744277</v>
       </c>
       <c r="V24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="W24" s="10">
-        <v>0.10747991888963403</v>
+        <v>8.8271240469868784E-2</v>
       </c>
       <c r="X24" s="10">
-        <v>0.22027412635774316</v>
+        <v>0.19956047987900999</v>
       </c>
       <c r="Y24" s="10">
-        <v>0.17842401235032268</v>
+        <v>0.14163192735258112</v>
       </c>
       <c r="Z24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AA24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AB24" s="10">
         <v>0</v>
       </c>
       <c r="AC24" s="10">
-        <v>0.29324667103783392</v>
+        <v>0.28749179924799778</v>
       </c>
       <c r="AD24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AE24" s="20">
-        <v>0.1086066205416437</v>
+        <v>9.1439499878104014E-2</v>
       </c>
       <c r="AF24" s="20">
-        <v>0.18413276459697114</v>
+        <v>0.18221300552363462</v>
       </c>
       <c r="AG24" s="20">
-        <v>0.44622384208498311</v>
+        <v>0.37485543479182903</v>
       </c>
       <c r="AH24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AI24" s="20">
-        <v>1.6364844392778521E-2</v>
+        <v>1.0599949054125677E-2</v>
       </c>
       <c r="AJ24" s="20">
-        <v>1.5624391981512975E-2</v>
+        <v>2.3397197622143442E-2</v>
       </c>
       <c r="AK24" s="20">
-        <v>0.26310150203699073</v>
+        <v>0.26754712809232362</v>
       </c>
       <c r="AL24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AM24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AN24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AO24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="AP24" s="10">
-        <v>0.34801337302759483</v>
+        <v>0.33091048322124222</v>
       </c>
       <c r="DG24" s="11"/>
     </row>
@@ -4114,10 +4118,10 @@
         <v>40</v>
       </c>
       <c r="C25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="D25" s="10">
-        <v>2.5414182500518304E-2</v>
+        <v>2.7923994729849529E-2</v>
       </c>
       <c r="E25" s="10">
         <v>0</v>
@@ -4126,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
@@ -4138,7 +4142,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="10">
-        <v>2.3335668341276764E-2</v>
+        <v>1.7523944134338155E-2</v>
       </c>
       <c r="L25" s="10">
         <v>0</v>
@@ -4150,43 +4154,43 @@
         <v>0</v>
       </c>
       <c r="O25" s="10">
-        <v>3.9346892134351864E-2</v>
+        <v>2.9477308697518877E-2</v>
       </c>
       <c r="P25" s="10">
-        <v>1.1663204138789929E-2</v>
+        <v>1.3680435587516724E-2</v>
       </c>
       <c r="Q25" s="10">
         <v>0</v>
       </c>
       <c r="R25" s="10">
-        <v>1.8945828477221555E-2</v>
+        <v>2.5068668227573376E-2</v>
       </c>
       <c r="S25" s="10">
         <v>0</v>
       </c>
       <c r="T25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="U25" s="10">
         <v>0</v>
       </c>
       <c r="V25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="W25" s="10">
-        <v>2.695538060174741E-2</v>
+        <v>2.2205879617100788E-2</v>
       </c>
       <c r="X25" s="10">
         <v>0</v>
       </c>
       <c r="Y25" s="10">
-        <v>9.6671797713389324E-2</v>
+        <v>9.4187805085969412E-2</v>
       </c>
       <c r="Z25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AA25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AB25" s="10">
         <v>0</v>
@@ -4195,19 +4199,19 @@
         <v>0</v>
       </c>
       <c r="AD25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AE25" s="20">
-        <v>2.5642891940333427E-2</v>
+        <v>1.7166013459077929E-2</v>
       </c>
       <c r="AF25" s="20">
         <v>0</v>
       </c>
       <c r="AG25" s="20">
-        <v>1.9694515393616913E-2</v>
+        <v>1.6300924504157356E-2</v>
       </c>
       <c r="AH25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AI25" s="20">
         <v>0</v>
@@ -4219,19 +4223,19 @@
         <v>0</v>
       </c>
       <c r="AL25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AM25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AN25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AO25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="AP25" s="10">
-        <v>6.629431731802706E-3</v>
+        <v>6.3962594512994558E-3</v>
       </c>
       <c r="DG25" s="11"/>
     </row>
@@ -4372,34 +4376,34 @@
         <v>44</v>
       </c>
       <c r="C27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="D27" s="10">
-        <v>0.42752347596213275</v>
+        <v>0.38693124723221828</v>
       </c>
       <c r="E27" s="10">
-        <v>2.0280776196689592E-2</v>
+        <v>3.047794836363683E-2</v>
       </c>
       <c r="F27" s="10">
-        <v>0.24213069833258843</v>
+        <v>0.2598130608486765</v>
       </c>
       <c r="G27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="H27" s="10">
         <v>0</v>
       </c>
       <c r="I27" s="10">
-        <v>0.2517591604319005</v>
+        <v>0.21868576949137514</v>
       </c>
       <c r="J27" s="10">
-        <v>6.9644885661285988E-2</v>
+        <v>7.4672278662223771E-2</v>
       </c>
       <c r="K27" s="10">
-        <v>0.62163897856544104</v>
+        <v>0.78708472888978465</v>
       </c>
       <c r="L27" s="10">
-        <v>0.32842611043468889</v>
+        <v>0.30329928783292098</v>
       </c>
       <c r="M27" s="10">
         <v>0</v>
@@ -4408,88 +4412,88 @@
         <v>0</v>
       </c>
       <c r="O27" s="10">
-        <v>0.51724897050803709</v>
+        <v>0.46282566886886345</v>
       </c>
       <c r="P27" s="10">
-        <v>4.7670895566727399E-2</v>
+        <v>3.6598116252931717E-2</v>
       </c>
       <c r="Q27" s="10">
-        <v>0.17282325093966425</v>
+        <v>0.16160187938106726</v>
       </c>
       <c r="R27" s="10">
-        <v>0.10177355115188068</v>
+        <v>8.1948851353859459E-2</v>
       </c>
       <c r="S27" s="10">
         <v>0</v>
       </c>
       <c r="T27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="U27" s="10">
-        <v>2.932158551655752E-2</v>
+        <v>1.7508717233209781E-2</v>
       </c>
       <c r="V27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="W27" s="10">
-        <v>0.6053833695832681</v>
+        <v>0.51769000981448265</v>
       </c>
       <c r="X27" s="10">
-        <v>0.21375783677576052</v>
+        <v>0.15002152304089991</v>
       </c>
       <c r="Y27" s="10">
-        <v>0.3586292760317375</v>
+        <v>0.31153199820623595</v>
       </c>
       <c r="Z27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AA27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AB27" s="10">
         <v>0</v>
       </c>
       <c r="AC27" s="10">
-        <v>5.3931090870580345E-2</v>
+        <v>5.4607660975053547E-2</v>
       </c>
       <c r="AD27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AE27" s="20">
-        <v>0.14462493045760588</v>
+        <v>0.14361679460566562</v>
       </c>
       <c r="AF27" s="20">
-        <v>1.0054161060837502E-2</v>
+        <v>4.6626766670884359E-3</v>
       </c>
       <c r="AG27" s="20">
-        <v>0.10501343880347851</v>
+        <v>8.4436829881912409E-2</v>
       </c>
       <c r="AH27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AI27" s="20">
-        <v>0.57271022775437064</v>
+        <v>0.51437737047954646</v>
       </c>
       <c r="AJ27" s="20">
-        <v>0.19459490774405377</v>
+        <v>0.17658114957827517</v>
       </c>
       <c r="AK27" s="20">
-        <v>5.4032876024943555E-2</v>
+        <v>5.6999179212492326E-2</v>
       </c>
       <c r="AL27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AM27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AN27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AO27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="AP27" s="10">
-        <v>0.1080837099681915</v>
+        <v>0.10448559506895344</v>
       </c>
       <c r="DG27" s="11"/>
     </row>
@@ -4630,124 +4634,124 @@
         <v>70</v>
       </c>
       <c r="C29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="D29" s="10">
-        <v>0.15647181731284962</v>
+        <v>0.16813857606706978</v>
       </c>
       <c r="E29" s="10">
-        <v>0.24124887206569232</v>
+        <v>0.4074780259759197</v>
       </c>
       <c r="F29" s="10">
-        <v>0.43945466784358111</v>
+        <v>0.40788879414475943</v>
       </c>
       <c r="G29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="H29" s="10">
-        <v>0.28007240306959008</v>
+        <v>0.40467240425092182</v>
       </c>
       <c r="I29" s="10">
-        <v>0.29415117733767548</v>
+        <v>0.4122701301648149</v>
       </c>
       <c r="J29" s="10">
-        <v>0.16469609878796049</v>
+        <v>4.0899255979277849E-2</v>
       </c>
       <c r="K29" s="10">
-        <v>0.20207549527120519</v>
+        <v>8.2117709368063799E-2</v>
       </c>
       <c r="L29" s="10">
-        <v>0.42102956973717198</v>
+        <v>0.53489887715506612</v>
       </c>
       <c r="M29" s="10">
-        <v>0.80473579956214891</v>
+        <v>0.8531428190571626</v>
       </c>
       <c r="N29" s="10">
-        <v>0.30108757751662202</v>
+        <v>0.26191141761349673</v>
       </c>
       <c r="O29" s="10">
-        <v>0.36995448682474413</v>
+        <v>0.45990412759835558</v>
       </c>
       <c r="P29" s="10">
-        <v>0.61720086595451162</v>
+        <v>0.64869017932325623</v>
       </c>
       <c r="Q29" s="10">
-        <v>0.22274966299300064</v>
+        <v>0.37430050704722795</v>
       </c>
       <c r="R29" s="10">
-        <v>0.26474365514753984</v>
+        <v>0.33183317640854409</v>
       </c>
       <c r="S29" s="10">
-        <v>0.67664359876631741</v>
+        <v>0.6534125448059217</v>
       </c>
       <c r="T29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="U29" s="10">
-        <v>0.43188053968099932</v>
+        <v>0.5248655712203133</v>
       </c>
       <c r="V29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="W29" s="10">
-        <v>0.2529969899364099</v>
+        <v>0.36218477404544025</v>
       </c>
       <c r="X29" s="10">
-        <v>0.32962404985370602</v>
+        <v>0.49143134718460757</v>
       </c>
       <c r="Y29" s="10">
-        <v>0.31435978615688148</v>
+        <v>0.40302511656035922</v>
       </c>
       <c r="Z29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AA29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AB29" s="10">
-        <v>0.98153435046734827</v>
+        <v>0.98475185004846022</v>
       </c>
       <c r="AC29" s="10">
-        <v>0.60015901868976906</v>
+        <v>0.59721102449391283</v>
       </c>
       <c r="AD29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AE29" s="20">
-        <v>0.60201742251093104</v>
+        <v>0.66286171742838507</v>
       </c>
       <c r="AF29" s="20">
-        <v>0.31166361227834627</v>
+        <v>0.32924371702439087</v>
       </c>
       <c r="AG29" s="20">
-        <v>0.18481030105783086</v>
+        <v>0.29523819660782713</v>
       </c>
       <c r="AH29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AI29" s="20">
-        <v>0.3362042557028293</v>
+        <v>0.42806424527863629</v>
       </c>
       <c r="AJ29" s="20">
-        <v>0.49794913263535506</v>
+        <v>0.56602333893903345</v>
       </c>
       <c r="AK29" s="20">
-        <v>0.63755948046706379</v>
+        <v>0.63691593602148244</v>
       </c>
       <c r="AL29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AM29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AN29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AO29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="AP29" s="10">
-        <v>0.3899399826166125</v>
+        <v>0.41166352819502167</v>
       </c>
       <c r="DG29" s="12"/>
     </row>
@@ -4759,10 +4763,10 @@
         <v>50</v>
       </c>
       <c r="C30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="D30" s="10">
-        <v>0</v>
+        <v>1.3166439564978479E-3</v>
       </c>
       <c r="E30" s="10">
         <v>0</v>
@@ -4771,16 +4775,16 @@
         <v>0</v>
       </c>
       <c r="G30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="H30" s="10">
-        <v>0</v>
+        <v>4.1526875381217018E-4</v>
       </c>
       <c r="I30" s="10">
         <v>0</v>
       </c>
       <c r="J30" s="10">
-        <v>0</v>
+        <v>1.0199004453873325E-3</v>
       </c>
       <c r="K30" s="10">
         <v>0</v>
@@ -4792,13 +4796,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="10">
-        <v>0</v>
+        <v>1.3626949661293996E-4</v>
       </c>
       <c r="O30" s="10">
-        <v>0</v>
+        <v>1.6374661880790477E-3</v>
       </c>
       <c r="P30" s="10">
-        <v>0</v>
+        <v>2.0333424112008421E-3</v>
       </c>
       <c r="Q30" s="10">
         <v>0</v>
@@ -4810,13 +4814,13 @@
         <v>0</v>
       </c>
       <c r="T30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="U30" s="10">
-        <v>0</v>
+        <v>8.5451759542766466E-6</v>
       </c>
       <c r="V30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="W30" s="10">
         <v>0</v>
@@ -4828,34 +4832,34 @@
         <v>0</v>
       </c>
       <c r="Z30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AA30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AB30" s="10">
         <v>0</v>
       </c>
       <c r="AC30" s="10">
-        <v>0</v>
+        <v>1.0387837058397856E-3</v>
       </c>
       <c r="AD30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AE30" s="10">
-        <v>0</v>
+        <v>1.6771704909439802E-5</v>
       </c>
       <c r="AF30" s="10">
-        <v>0</v>
+        <v>2.2144526636962056E-3</v>
       </c>
       <c r="AG30" s="10">
         <v>0</v>
       </c>
       <c r="AH30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AI30" s="10">
-        <v>0</v>
+        <v>1.2848020281046008E-2</v>
       </c>
       <c r="AJ30" s="10">
         <v>0</v>
@@ -4864,19 +4868,19 @@
         <v>0</v>
       </c>
       <c r="AL30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AM30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AN30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AO30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="AP30" s="10">
-        <v>0</v>
+        <v>1.5264781755392933E-3</v>
       </c>
       <c r="DG30" s="12"/>
     </row>
@@ -4888,124 +4892,124 @@
         <v>52</v>
       </c>
       <c r="C31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="D31" s="10">
-        <v>0</v>
+        <v>2.4042397592519184E-4</v>
       </c>
       <c r="E31" s="10">
-        <v>0</v>
+        <v>8.4081877441351833E-3</v>
       </c>
       <c r="F31" s="10">
-        <v>0</v>
+        <v>4.47758881600583E-3</v>
       </c>
       <c r="G31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="H31" s="10">
         <v>0</v>
       </c>
       <c r="I31" s="10">
-        <v>0</v>
+        <v>9.1380033575667076E-3</v>
       </c>
       <c r="J31" s="10">
-        <v>0</v>
+        <v>3.7111816909101855E-2</v>
       </c>
       <c r="K31" s="10">
-        <v>0</v>
+        <v>3.3670222467799035E-2</v>
       </c>
       <c r="L31" s="10">
-        <v>0</v>
+        <v>1.113476317070688E-2</v>
       </c>
       <c r="M31" s="10">
-        <v>0</v>
+        <v>3.1820348593619048E-3</v>
       </c>
       <c r="N31" s="10">
-        <v>0</v>
+        <v>1.1824371159497032E-2</v>
       </c>
       <c r="O31" s="10">
-        <v>0</v>
+        <v>3.4327919382857426E-3</v>
       </c>
       <c r="P31" s="10">
-        <v>0</v>
+        <v>9.0997427931697669E-3</v>
       </c>
       <c r="Q31" s="10">
-        <v>0</v>
+        <v>8.9160837396307297E-4</v>
       </c>
       <c r="R31" s="10">
-        <v>0</v>
+        <v>3.1809781728338858E-3</v>
       </c>
       <c r="S31" s="10">
-        <v>0</v>
+        <v>4.8728589786560163E-3</v>
       </c>
       <c r="T31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="U31" s="10">
-        <v>0</v>
+        <v>3.278801768409164E-3</v>
       </c>
       <c r="V31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="W31" s="10">
-        <v>0</v>
+        <v>5.8957245204014075E-3</v>
       </c>
       <c r="X31" s="10">
-        <v>0</v>
+        <v>3.2891769910307934E-3</v>
       </c>
       <c r="Y31" s="10">
-        <v>0</v>
+        <v>3.7858841559402856E-3</v>
       </c>
       <c r="Z31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AA31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AB31" s="10">
         <v>0</v>
       </c>
       <c r="AC31" s="10">
-        <v>0</v>
+        <v>7.5087587931429028E-3</v>
       </c>
       <c r="AD31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AE31" s="10">
-        <v>0</v>
+        <v>4.5627110085032611E-3</v>
       </c>
       <c r="AF31" s="10">
-        <v>0</v>
+        <v>2.3905103147238248E-4</v>
       </c>
       <c r="AG31" s="10">
-        <v>0</v>
+        <v>1.0814598153898966E-3</v>
       </c>
       <c r="AH31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AI31" s="10">
-        <v>0</v>
+        <v>6.3419339653210751E-4</v>
       </c>
       <c r="AJ31" s="10">
-        <v>0</v>
+        <v>1.1184637454825076E-3</v>
       </c>
       <c r="AK31" s="10">
-        <v>0</v>
+        <v>4.6799687556756103E-3</v>
       </c>
       <c r="AL31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AM31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AN31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AO31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="AP31" s="10">
-        <v>0</v>
+        <v>1.2565030349614415E-2</v>
       </c>
       <c r="DG31" s="12"/>
     </row>
@@ -5146,64 +5150,64 @@
         <v>75</v>
       </c>
       <c r="C33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="D33" s="10">
-        <v>0.22960514627370454</v>
+        <v>0.2300619292090508</v>
       </c>
       <c r="E33" s="10">
-        <v>4.9097186228988848E-3</v>
+        <v>4.4790128322856433E-3</v>
       </c>
       <c r="F33" s="10">
-        <v>0.17874104210205835</v>
+        <v>0.19062245863501942</v>
       </c>
       <c r="G33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="H33" s="10">
-        <v>0.53516569738999564</v>
+        <v>0.38661715930802054</v>
       </c>
       <c r="I33" s="10">
-        <v>2.0229321142395895E-2</v>
+        <v>2.1240184707851918E-2</v>
       </c>
       <c r="J33" s="10">
-        <v>1.4094934338016724E-2</v>
+        <v>1.6344247252751166E-2</v>
       </c>
       <c r="K33" s="10">
-        <v>1.6774414394045815E-2</v>
+        <v>1.6313781299804941E-2</v>
       </c>
       <c r="L33" s="10">
         <v>0</v>
       </c>
       <c r="M33" s="10">
-        <v>5.4157903900161612E-2</v>
+        <v>5.3428881664231091E-2</v>
       </c>
       <c r="N33" s="10">
-        <v>6.2228572950025846E-2</v>
+        <v>5.9841854163694606E-2</v>
       </c>
       <c r="O33" s="10">
         <v>0</v>
       </c>
       <c r="P33" s="10">
-        <v>8.6098368416373285E-3</v>
+        <v>8.0420859165798077E-3</v>
       </c>
       <c r="Q33" s="10">
-        <v>8.1957661899039913E-2</v>
+        <v>7.7114386421996542E-2</v>
       </c>
       <c r="R33" s="10">
-        <v>1.7521527546865417E-3</v>
+        <v>2.0609680904946962E-3</v>
       </c>
       <c r="S33" s="10">
-        <v>1.4707802534048447E-3</v>
+        <v>1.4676465256834395E-3</v>
       </c>
       <c r="T33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="U33" s="10">
-        <v>4.1103135684841911E-2</v>
+        <v>3.5914080140322636E-2</v>
       </c>
       <c r="V33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="W33" s="10">
         <v>0</v>
@@ -5215,31 +5219,31 @@
         <v>0</v>
       </c>
       <c r="Z33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AA33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AB33" s="10">
         <v>0</v>
       </c>
       <c r="AC33" s="10">
-        <v>1.0229093776943428E-2</v>
+        <v>9.7441667993268134E-3</v>
       </c>
       <c r="AD33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AE33" s="20">
-        <v>8.8120936741382244E-3</v>
+        <v>8.227640715157471E-3</v>
       </c>
       <c r="AF33" s="20">
-        <v>0.27103586100600024</v>
+        <v>0.27402335993057869</v>
       </c>
       <c r="AG33" s="20">
-        <v>1.9057236203893118E-3</v>
+        <v>1.7151015716015666E-3</v>
       </c>
       <c r="AH33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AI33" s="20">
         <v>0</v>
@@ -5248,22 +5252,22 @@
         <v>0</v>
       </c>
       <c r="AK33" s="20">
-        <v>7.4728375421967853E-3</v>
+        <v>1.7801113601544561E-2</v>
       </c>
       <c r="AL33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AM33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AN33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AO33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="AP33" s="10">
-        <v>3.1762383224260268E-2</v>
+        <v>3.1716052556899847E-2</v>
       </c>
       <c r="DG33" s="16"/>
     </row>
@@ -5533,124 +5537,124 @@
         <v>32</v>
       </c>
       <c r="C36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="D36" s="10">
-        <v>2.6671836087890404E-2</v>
+        <v>7.954097300076313E-3</v>
       </c>
       <c r="E36" s="10">
-        <v>4.5131797831629641E-2</v>
+        <v>2.6606023661408417E-2</v>
       </c>
       <c r="F36" s="10">
-        <v>5.4400610461417982E-2</v>
+        <v>7.2308911971074197E-2</v>
       </c>
       <c r="G36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="H36" s="10">
-        <v>0.22090868486755089</v>
+        <v>0.20592092231948497</v>
       </c>
       <c r="I36" s="10">
         <v>0</v>
       </c>
       <c r="J36" s="10">
-        <v>2.9188299133307671E-2</v>
+        <v>1.0782717048399988E-2</v>
       </c>
       <c r="K36" s="10">
-        <v>4.3037391982029438E-2</v>
+        <v>7.1037980199091674E-2</v>
       </c>
       <c r="L36" s="10">
-        <v>3.7190972777495383E-2</v>
+        <v>5.6003514134172219E-2</v>
       </c>
       <c r="M36" s="10">
-        <v>0.12820914546237097</v>
+        <v>0.19919909840567773</v>
       </c>
       <c r="N36" s="10">
-        <v>5.6257736227318646E-2</v>
+        <v>0.10512135147277678</v>
       </c>
       <c r="O36" s="10">
         <v>0</v>
       </c>
       <c r="P36" s="10">
-        <v>9.9564687559475021E-2</v>
+        <v>6.578623352008614E-2</v>
       </c>
       <c r="Q36" s="10">
-        <v>6.7761473662515948E-2</v>
+        <v>3.4532975518057681E-2</v>
       </c>
       <c r="R36" s="10">
-        <v>4.4327847133909346E-2</v>
+        <v>4.4570185446382082E-2</v>
       </c>
       <c r="S36" s="10">
-        <v>0.29066074568275641</v>
+        <v>0.33280554792553552</v>
       </c>
       <c r="T36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="U36" s="10">
-        <v>0.11923707409049086</v>
+        <v>0.10915134394963434</v>
       </c>
       <c r="V36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="W36" s="10">
         <v>0</v>
       </c>
       <c r="X36" s="10">
-        <v>0.17215935714583952</v>
+        <v>0.16770887602691506</v>
       </c>
       <c r="Y36" s="10">
-        <v>8.3205431712358377E-2</v>
+        <v>8.3271323393786054E-2</v>
       </c>
       <c r="Z36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AA36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AB36" s="10">
-        <v>0.23319027293043162</v>
+        <v>0.31662787996654551</v>
       </c>
       <c r="AC36" s="10">
-        <v>9.2634253087691673E-2</v>
+        <v>4.3835009646710089E-2</v>
       </c>
       <c r="AD36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AE36" s="21">
-        <v>2.2007655686795528E-2</v>
+        <v>1.5570970844945234E-2</v>
       </c>
       <c r="AF36" s="21">
-        <v>0.15017402435334426</v>
+        <v>0.20700484401269542</v>
       </c>
       <c r="AG36" s="21">
-        <v>5.7972569332444143E-2</v>
+        <v>4.3709612039274884E-2</v>
       </c>
       <c r="AH36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AI36" s="21">
-        <v>2.7314849356581534E-2</v>
+        <v>2.1066584284585004E-2</v>
       </c>
       <c r="AJ36" s="21">
-        <v>0.17518414897736326</v>
+        <v>0.11030763705066582</v>
       </c>
       <c r="AK36" s="21">
-        <v>1.4840562452086752E-2</v>
+        <v>1.4753443800771553E-2</v>
       </c>
       <c r="AL36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AM36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AN36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AO36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="AP36" s="10">
-        <v>6.736688066584702E-2</v>
+        <v>6.2923344497889333E-2</v>
       </c>
       <c r="DG36" s="11"/>
     </row>
@@ -5662,124 +5666,124 @@
         <v>38</v>
       </c>
       <c r="C37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="D37" s="10">
-        <v>0.30639683822511476</v>
+        <v>0.34415682659406671</v>
       </c>
       <c r="E37" s="10">
-        <v>0.45704221839922754</v>
+        <v>0.32598756783825134</v>
       </c>
       <c r="F37" s="10">
-        <v>7.9832607612464287E-2</v>
+        <v>7.3731497357451867E-2</v>
       </c>
       <c r="G37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="H37" s="10">
         <v>0</v>
       </c>
       <c r="I37" s="10">
-        <v>0.50871274816937861</v>
+        <v>0.4219077613894634</v>
       </c>
       <c r="J37" s="10">
-        <v>0.62030003435592107</v>
+        <v>0.89522621176974593</v>
       </c>
       <c r="K37" s="10">
-        <v>0.18461053684162762</v>
+        <v>0.30773120057199821</v>
       </c>
       <c r="L37" s="10">
-        <v>0.17588866241793183</v>
+        <v>9.2118608308088171E-2</v>
       </c>
       <c r="M37" s="10">
-        <v>7.6343454059028079E-2</v>
+        <v>4.988964989148191E-2</v>
       </c>
       <c r="N37" s="10">
-        <v>0.52219995384129358</v>
+        <v>0.38764140704464678</v>
       </c>
       <c r="O37" s="10">
-        <v>1.6091753110864086E-2</v>
+        <v>7.0512387189534337E-3</v>
       </c>
       <c r="P37" s="10">
-        <v>0.34937426598116378</v>
+        <v>0.25538742015276072</v>
       </c>
       <c r="Q37" s="10">
-        <v>0.10310013857863436</v>
+        <v>0.14860085908986481</v>
       </c>
       <c r="R37" s="10">
-        <v>0.54814684694111659</v>
+        <v>0.52419510615856013</v>
       </c>
       <c r="S37" s="10">
-        <v>0.126211692732241</v>
+        <v>0.12678702125973537</v>
       </c>
       <c r="T37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="U37" s="10">
-        <v>0.55795079596726627</v>
+        <v>0.49301453170688392</v>
       </c>
       <c r="V37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="W37" s="10">
-        <v>8.4626283003462019E-2</v>
+        <v>9.6802721356827284E-2</v>
       </c>
       <c r="X37" s="10">
-        <v>7.9886207766255296E-2</v>
+        <v>0.14152774094974754</v>
       </c>
       <c r="Y37" s="10">
-        <v>0.28084326707176238</v>
+        <v>0.22647373371772112</v>
       </c>
       <c r="Z37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AA37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AB37" s="10">
         <v>0</v>
       </c>
       <c r="AC37" s="10">
-        <v>0.21535711034244703</v>
+        <v>0.21158580508512168</v>
       </c>
       <c r="AD37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AE37" s="21">
-        <v>0.25524597778687846</v>
+        <v>0.24411095287667106</v>
       </c>
       <c r="AF37" s="21">
-        <v>0.19504423315158881</v>
+        <v>0.17027611422746525</v>
       </c>
       <c r="AG37" s="21">
-        <v>0.34177010494230176</v>
+        <v>0.31477821350116558</v>
       </c>
       <c r="AH37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AI37" s="21">
-        <v>1.7783670106281485E-2</v>
+        <v>1.3428136694518414E-2</v>
       </c>
       <c r="AJ37" s="21">
-        <v>5.2741159109469075E-2</v>
+        <v>5.8904109935927082E-2</v>
       </c>
       <c r="AK37" s="21">
-        <v>0.45650870564832197</v>
+        <v>0.41212740681924082</v>
       </c>
       <c r="AL37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AM37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AN37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AO37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="AP37" s="10">
-        <v>0.41585603944492661</v>
+        <v>0.40361258709306386</v>
       </c>
       <c r="DG37" s="11"/>
     </row>
@@ -5791,28 +5795,28 @@
         <v>40</v>
       </c>
       <c r="C38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="D38" s="10">
-        <v>1.7964465437274282E-2</v>
+        <v>1.7456164635961908E-2</v>
       </c>
       <c r="E38" s="10">
-        <v>1.4233027433254743E-3</v>
+        <v>1.7580839649752511E-3</v>
       </c>
       <c r="F38" s="10">
-        <v>7.7248294450157129E-2</v>
+        <v>8.5796063513005991E-2</v>
       </c>
       <c r="G38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="H38" s="10">
-        <v>0.10871516530873603</v>
+        <v>9.8633688966712971E-2</v>
       </c>
       <c r="I38" s="10">
         <v>0</v>
       </c>
       <c r="J38" s="10">
-        <v>1.4531246546959067E-3</v>
+        <v>1.393151357307752E-3</v>
       </c>
       <c r="K38" s="10">
         <v>0</v>
@@ -5833,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="10">
-        <v>6.5381175083229215E-3</v>
+        <v>8.9477567338373965E-3</v>
       </c>
       <c r="R38" s="10">
         <v>0</v>
@@ -5842,16 +5846,16 @@
         <v>0</v>
       </c>
       <c r="T38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="U38" s="10">
         <v>0</v>
       </c>
       <c r="V38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="W38" s="10">
-        <v>6.1479885564156234E-2</v>
+        <v>3.9251468124629658E-2</v>
       </c>
       <c r="X38" s="10">
         <v>0</v>
@@ -5860,10 +5864,10 @@
         <v>0</v>
       </c>
       <c r="Z38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AA38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AB38" s="10">
         <v>0</v>
@@ -5872,19 +5876,19 @@
         <v>0</v>
       </c>
       <c r="AD38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AE38" s="21">
         <v>0</v>
       </c>
       <c r="AF38" s="21">
-        <v>5.4885420263416113E-2</v>
+        <v>5.5126046470933041E-2</v>
       </c>
       <c r="AG38" s="21">
         <v>0</v>
       </c>
       <c r="AH38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AI38" s="21">
         <v>0</v>
@@ -5896,19 +5900,19 @@
         <v>0</v>
       </c>
       <c r="AL38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AM38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AN38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AO38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="AP38" s="10">
-        <v>2.9625969546928938E-3</v>
+        <v>3.0550527532233443E-3</v>
       </c>
       <c r="DG38" s="11"/>
     </row>
@@ -5920,124 +5924,124 @@
         <v>70</v>
       </c>
       <c r="C39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="D39" s="10">
-        <v>0.6489668602497205</v>
+        <v>0.630432911469895</v>
       </c>
       <c r="E39" s="10">
-        <v>0.49640268102581742</v>
+        <v>0.64564832453536469</v>
       </c>
       <c r="F39" s="10">
-        <v>0.78851848747596021</v>
+        <v>0.76816352715846836</v>
       </c>
       <c r="G39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="H39" s="10">
-        <v>0.67037614982371341</v>
+        <v>0.69544538871380213</v>
       </c>
       <c r="I39" s="10">
-        <v>0.49128725183062144</v>
+        <v>0.57809223861053682</v>
       </c>
       <c r="J39" s="10">
-        <v>0.34905854185607554</v>
+        <v>9.259791982454596E-2</v>
       </c>
       <c r="K39" s="10">
-        <v>0.77235207117634286</v>
+        <v>0.62123081922890999</v>
       </c>
       <c r="L39" s="10">
-        <v>0.78692036480457295</v>
+        <v>0.85187787755773936</v>
       </c>
       <c r="M39" s="10">
-        <v>0.79544740047860074</v>
+        <v>0.75091125170284001</v>
       </c>
       <c r="N39" s="10">
-        <v>0.42154230993138764</v>
+        <v>0.50723724148257598</v>
       </c>
       <c r="O39" s="10">
-        <v>0.98390824688913603</v>
+        <v>0.99294876128104681</v>
       </c>
       <c r="P39" s="10">
-        <v>0.55106104645936138</v>
+        <v>0.67882634632715311</v>
       </c>
       <c r="Q39" s="10">
-        <v>0.82260027025052673</v>
+        <v>0.80791840865824016</v>
       </c>
       <c r="R39" s="10">
-        <v>0.40752530592497421</v>
+        <v>0.43123470839505762</v>
       </c>
       <c r="S39" s="10">
-        <v>0.58312756158500245</v>
+        <v>0.54040743081472931</v>
       </c>
       <c r="T39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="U39" s="10">
-        <v>0.32281212994224273</v>
+        <v>0.39783412434348148</v>
       </c>
       <c r="V39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="W39" s="10">
-        <v>0.85389383143238196</v>
+        <v>0.86394581051854324</v>
       </c>
       <c r="X39" s="10">
-        <v>0.74795443508790538</v>
+        <v>0.69076338302333717</v>
       </c>
       <c r="Y39" s="10">
-        <v>0.63595130121587939</v>
+        <v>0.69025494288849276</v>
       </c>
       <c r="Z39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AA39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AB39" s="10">
-        <v>0.76680972706956885</v>
+        <v>0.68337212003345427</v>
       </c>
       <c r="AC39" s="10">
-        <v>0.69200863656986122</v>
+        <v>0.74457918526816835</v>
       </c>
       <c r="AD39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AE39" s="21">
-        <v>0.72274636652632596</v>
+        <v>0.74031807627838364</v>
       </c>
       <c r="AF39" s="21">
-        <v>0.59989632223165068</v>
+        <v>0.56759299528890572</v>
       </c>
       <c r="AG39" s="21">
-        <v>0.60025732572525403</v>
+        <v>0.64151217445955955</v>
       </c>
       <c r="AH39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AI39" s="21">
-        <v>0.95490148053713719</v>
+        <v>0.96550527902089656</v>
       </c>
       <c r="AJ39" s="21">
-        <v>0.77207469191316769</v>
+        <v>0.8307882530134072</v>
       </c>
       <c r="AK39" s="21">
-        <v>0.52865073189959144</v>
+        <v>0.57311914937998754</v>
       </c>
       <c r="AL39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AM39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AN39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AO39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="AP39" s="10">
-        <v>0.51381448293453325</v>
+        <v>0.53040901565582366</v>
       </c>
       <c r="DG39" s="18"/>
     </row>
